--- a/AAII_Financials/Quarterly/HSCS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HSCS_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="92">
   <si>
     <t>HSCS</t>
   </si>
@@ -656,79 +656,87 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45322</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45230</v>
+      </c>
+      <c r="F7" s="2">
         <v>45138</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45046</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>44957</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44865</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44773</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44681</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44592</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44500</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44408</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44316</v>
       </c>
-      <c r="N7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="O7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -771,19 +779,25 @@
       <c r="P8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3">
+        <v>0</v>
+      </c>
+      <c r="R8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F9" s="3">
-        <v>0</v>
+      <c r="D9" s="3">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>3</v>
@@ -791,43 +805,49 @@
       <c r="H9" s="3">
         <v>0</v>
       </c>
-      <c r="I9" s="3">
-        <v>0</v>
+      <c r="I9" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J9" s="3">
         <v>0</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>3</v>
+      <c r="K9" s="3">
+        <v>0</v>
       </c>
       <c r="L9" s="3">
         <v>0</v>
       </c>
-      <c r="M9" s="3">
-        <v>0</v>
-      </c>
-      <c r="N9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O9" s="3" t="s">
-        <v>3</v>
+      <c r="M9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N9" s="3">
+        <v>0</v>
+      </c>
+      <c r="O9" s="3">
+        <v>0</v>
       </c>
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F10" s="3">
-        <v>0</v>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>3</v>
@@ -835,32 +855,38 @@
       <c r="H10" s="3">
         <v>0</v>
       </c>
-      <c r="I10" s="3">
-        <v>0</v>
+      <c r="I10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J10" s="3">
         <v>0</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
+      <c r="K10" s="3">
+        <v>0</v>
       </c>
       <c r="L10" s="3">
         <v>0</v>
       </c>
-      <c r="M10" s="3">
-        <v>0</v>
-      </c>
-      <c r="N10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O10" s="3" t="s">
-        <v>3</v>
+      <c r="M10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N10" s="3">
+        <v>0</v>
+      </c>
+      <c r="O10" s="3">
+        <v>0</v>
       </c>
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -877,52 +903,60 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="E12" s="3">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="F12" s="3">
         <v>600</v>
       </c>
       <c r="G12" s="3">
+        <v>500</v>
+      </c>
+      <c r="H12" s="3">
+        <v>600</v>
+      </c>
+      <c r="I12" s="3">
         <v>800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>1400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>1600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>600</v>
       </c>
-      <c r="N12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -965,19 +999,25 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G14" s="3">
         <v>0</v>
@@ -989,7 +1029,7 @@
         <v>0</v>
       </c>
       <c r="J14" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1000,17 +1040,23 @@
       <c r="M14" s="3">
         <v>0</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
+      <c r="N14" s="3">
+        <v>-300</v>
+      </c>
+      <c r="O14" s="3">
+        <v>0</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1053,8 +1099,14 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1068,13 +1120,15 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
-        <v>1300</v>
+      <c r="D17" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E17" s="3">
         <v>1600</v>
@@ -1083,37 +1137,43 @@
         <v>1300</v>
       </c>
       <c r="G17" s="3">
+        <v>1600</v>
+      </c>
+      <c r="H17" s="3">
+        <v>1300</v>
+      </c>
+      <c r="I17" s="3">
         <v>1800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>1400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>2000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>2500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>1000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>800</v>
       </c>
-      <c r="N17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1127,37 +1187,43 @@
         <v>-1300</v>
       </c>
       <c r="G18" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="H18" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="I18" s="3">
         <v>-1800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-1400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-2000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-2500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-1000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-800</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1174,8 +1240,10 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1209,17 +1277,23 @@
       <c r="M20" s="3">
         <v>0</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O20" s="3" t="s">
-        <v>3</v>
+      <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
+        <v>0</v>
       </c>
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1233,45 +1307,51 @@
         <v>-1300</v>
       </c>
       <c r="G21" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="I21" s="3">
         <v>-1800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-1400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-2000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-2500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-1000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-800</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E22" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F22" s="3">
         <v>0</v>
@@ -1280,78 +1360,90 @@
         <v>0</v>
       </c>
       <c r="H22" s="3">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3">
         <v>100</v>
-      </c>
-      <c r="I22" s="3">
-        <v>100</v>
-      </c>
-      <c r="J22" s="3">
-        <v>300</v>
       </c>
       <c r="K22" s="3">
         <v>100</v>
       </c>
       <c r="L22" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="M22" s="3">
         <v>100</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O22" s="3" t="s">
-        <v>3</v>
+      <c r="N22" s="3">
+        <v>100</v>
+      </c>
+      <c r="O22" s="3">
+        <v>100</v>
       </c>
       <c r="P22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
+      <c r="D23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="F23" s="3">
         <v>-1400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-1600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-1300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-1800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-1600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-2100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-2800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-1000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-900</v>
       </c>
-      <c r="N23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1394,8 +1486,14 @@
       <c r="P24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1438,96 +1536,114 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
+      <c r="D26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="F26" s="3">
         <v>-1400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-1600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-1300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-1800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-1600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-2100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-2800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-1000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-900</v>
       </c>
-      <c r="N26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="F27" s="3">
         <v>-1400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-1600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-1300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-1800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-1600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-2100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-2800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-1000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-900</v>
       </c>
-      <c r="N27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1570,8 +1686,14 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1614,8 +1736,14 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1658,8 +1786,14 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1702,8 +1836,14 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1737,61 +1877,73 @@
       <c r="M32" s="3">
         <v>0</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O32" s="3" t="s">
-        <v>3</v>
+      <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
+        <v>0</v>
       </c>
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="F33" s="3">
         <v>-1400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-1600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-1300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-1800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-1600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-2100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-2800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-1000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-900</v>
       </c>
-      <c r="N33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1834,101 +1986,119 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="F35" s="3">
         <v>-1400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-1600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-1300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-1800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-1600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-2100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-2800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-1000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-900</v>
       </c>
-      <c r="N35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45322</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45230</v>
+      </c>
+      <c r="F38" s="2">
         <v>45138</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45046</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>44957</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44865</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44773</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44681</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44592</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44500</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44408</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44316</v>
       </c>
-      <c r="N38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="O38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1945,8 +2115,10 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1963,38 +2135,40 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E41" s="3">
+        <v>100</v>
+      </c>
+      <c r="F41" s="3">
         <v>600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>1700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>1900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>3100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>4300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>1300</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2007,8 +2181,14 @@
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2051,19 +2231,25 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>3</v>
+      <c r="D43" s="3">
+        <v>0</v>
       </c>
       <c r="E43" s="3">
         <v>0</v>
       </c>
-      <c r="F43" s="3">
-        <v>0</v>
+      <c r="F43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G43" s="3">
         <v>0</v>
@@ -2074,11 +2260,11 @@
       <c r="I43" s="3">
         <v>0</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
+      <c r="J43" s="3">
+        <v>0</v>
+      </c>
+      <c r="K43" s="3">
+        <v>0</v>
       </c>
       <c r="L43" s="3" t="s">
         <v>3</v>
@@ -2095,8 +2281,14 @@
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2121,11 +2313,11 @@
       <c r="J44" s="3">
         <v>700</v>
       </c>
-      <c r="K44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L44" s="3" t="s">
-        <v>3</v>
+      <c r="K44" s="3">
+        <v>700</v>
+      </c>
+      <c r="L44" s="3">
+        <v>700</v>
       </c>
       <c r="M44" s="3" t="s">
         <v>3</v>
@@ -2139,38 +2331,44 @@
       <c r="P44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>900</v>
+      </c>
+      <c r="E45" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F45" s="3">
         <v>800</v>
-      </c>
-      <c r="E45" s="3">
-        <v>400</v>
-      </c>
-      <c r="F45" s="3">
-        <v>300</v>
       </c>
       <c r="G45" s="3">
         <v>400</v>
       </c>
       <c r="H45" s="3">
+        <v>300</v>
+      </c>
+      <c r="I45" s="3">
+        <v>400</v>
+      </c>
+      <c r="J45" s="3">
         <v>500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>400</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2183,38 +2381,44 @@
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E46" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F46" s="3">
         <v>2000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>2700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>2900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>4100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>5400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>1900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>2400</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2227,8 +2431,14 @@
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2271,13 +2481,19 @@
       <c r="P47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="E48" s="3">
         <v>600</v>
@@ -2289,20 +2505,20 @@
         <v>600</v>
       </c>
       <c r="H48" s="3">
+        <v>600</v>
+      </c>
+      <c r="I48" s="3">
+        <v>600</v>
+      </c>
+      <c r="J48" s="3">
         <v>100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>200</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2315,8 +2531,14 @@
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2359,8 +2581,14 @@
       <c r="P49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3">
+        <v>0</v>
+      </c>
+      <c r="R49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2403,8 +2631,14 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2447,8 +2681,14 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2491,8 +2731,14 @@
       <c r="P52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3">
+        <v>0</v>
+      </c>
+      <c r="R52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2535,38 +2781,44 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>10800</v>
+      </c>
+      <c r="E54" s="3">
+        <v>2400</v>
+      </c>
+      <c r="F54" s="3">
         <v>2600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>3300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>3500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>4800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>5600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>2100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>2600</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2579,8 +2831,14 @@
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2597,8 +2855,10 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2615,38 +2875,40 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>400</v>
+      </c>
+      <c r="E57" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F57" s="3">
         <v>500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>1000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>400</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2659,8 +2921,14 @@
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2668,29 +2936,29 @@
         <v>500</v>
       </c>
       <c r="E58" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F58" s="3">
         <v>500</v>
       </c>
-      <c r="F58" s="3">
-        <v>100</v>
-      </c>
       <c r="G58" s="3">
-        <v>1100</v>
+        <v>500</v>
       </c>
       <c r="H58" s="3">
         <v>100</v>
       </c>
       <c r="I58" s="3">
+        <v>1100</v>
+      </c>
+      <c r="J58" s="3">
+        <v>100</v>
+      </c>
+      <c r="K58" s="3">
         <v>1600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>2600</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2703,37 +2971,43 @@
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>800</v>
+      </c>
+      <c r="E59" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F59" s="3">
         <v>900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>1200</v>
-      </c>
-      <c r="H59" s="3">
-        <v>1000</v>
-      </c>
-      <c r="I59" s="3">
-        <v>1100</v>
       </c>
       <c r="J59" s="3">
         <v>1000</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
+      <c r="K59" s="3">
+        <v>1100</v>
+      </c>
+      <c r="L59" s="3">
+        <v>1000</v>
       </c>
       <c r="M59" s="3" t="s">
         <v>3</v>
@@ -2747,38 +3021,44 @@
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E60" s="3">
+        <v>3500</v>
+      </c>
+      <c r="F60" s="3">
         <v>1900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>1800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>2000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>3100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>1500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>3500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>4100</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2791,38 +3071,44 @@
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3">
+        <v>0</v>
+      </c>
+      <c r="F61" s="3">
         <v>500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>500</v>
-      </c>
-      <c r="F61" s="3">
-        <v>1000</v>
-      </c>
-      <c r="G61" s="3">
-        <v>0</v>
       </c>
       <c r="H61" s="3">
         <v>1000</v>
       </c>
       <c r="I61" s="3">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3">
+        <v>1000</v>
+      </c>
+      <c r="K61" s="3">
         <v>4400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>2600</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -2835,37 +3121,43 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>500</v>
+      </c>
+      <c r="E62" s="3">
+        <v>500</v>
+      </c>
+      <c r="F62" s="3">
         <v>700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>200</v>
       </c>
-      <c r="J62" s="3">
-        <v>0</v>
-      </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
+      <c r="L62" s="3">
+        <v>0</v>
       </c>
       <c r="M62" s="3" t="s">
         <v>3</v>
@@ -2879,8 +3171,14 @@
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2923,8 +3221,14 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2967,8 +3271,14 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3011,38 +3321,44 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E66" s="3">
+        <v>4000</v>
+      </c>
+      <c r="F66" s="3">
         <v>3100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>3100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>3700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>3700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>2700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>8100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>6700</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3055,8 +3371,14 @@
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3073,8 +3395,10 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3117,8 +3441,14 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3161,8 +3491,14 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3205,8 +3541,14 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3249,38 +3591,44 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-65500</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-63900</v>
+      </c>
+      <c r="F72" s="3">
         <v>-62100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-60800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-59100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-57800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-56000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-54400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-52300</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3293,8 +3641,14 @@
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3337,8 +3691,14 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3381,8 +3741,14 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3425,38 +3791,44 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3">
+      <c r="D76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E76" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="F76" s="3">
         <v>-500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>-300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>1100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>2900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>-6100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>-4100</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3469,8 +3841,14 @@
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3513,101 +3891,119 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45322</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45230</v>
+      </c>
+      <c r="F80" s="2">
         <v>45138</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45046</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>44957</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44865</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44773</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44681</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44592</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44500</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44408</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44316</v>
       </c>
-      <c r="N80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="O80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="F81" s="3">
         <v>-1400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-1600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-1300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-1800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-1600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-2100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-2800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-1000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-900</v>
       </c>
-      <c r="N81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3624,8 +4020,10 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3659,17 +4057,23 @@
       <c r="M83" s="3">
         <v>0</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O83" s="3" t="s">
-        <v>3</v>
+      <c r="N83" s="3">
+        <v>0</v>
+      </c>
+      <c r="O83" s="3">
+        <v>0</v>
       </c>
       <c r="P83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3712,8 +4116,14 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3756,8 +4166,14 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3800,8 +4216,14 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3844,8 +4266,14 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3888,52 +4316,64 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="F89" s="3">
         <v>-1400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-1900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-1000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-1100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-1800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-1200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-2500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-700</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3950,8 +4390,10 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3982,11 +4424,11 @@
       <c r="L91" s="3">
         <v>0</v>
       </c>
-      <c r="M91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N91" s="3" t="s">
-        <v>3</v>
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
+        <v>0</v>
       </c>
       <c r="O91" s="3" t="s">
         <v>3</v>
@@ -3994,8 +4436,14 @@
       <c r="P91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4038,8 +4486,14 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4082,8 +4536,14 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -4117,17 +4577,23 @@
       <c r="M94" s="3">
         <v>0</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
+      <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
+        <v>0</v>
       </c>
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4144,8 +4610,10 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4188,8 +4656,14 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4232,8 +4706,14 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4276,8 +4756,14 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4320,52 +4806,64 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E100" s="3">
+        <v>500</v>
+      </c>
+      <c r="F100" s="3">
         <v>300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>1600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>5200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>3100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>1100</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>500</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4408,48 +4906,60 @@
       <c r="P101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-1100</v>
+        <v>7000</v>
       </c>
       <c r="E102" s="3">
-        <v>-300</v>
+        <v>-500</v>
       </c>
       <c r="F102" s="3">
         <v>-1100</v>
       </c>
       <c r="G102" s="3">
+        <v>-300</v>
+      </c>
+      <c r="H102" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="I102" s="3">
         <v>-1200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>3400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-200</v>
       </c>
-      <c r="N102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/HSCS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HSCS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="92">
   <si>
     <t>HSCS</t>
   </si>
@@ -1127,8 +1127,8 @@
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>3</v>
+      <c r="D17" s="3">
+        <v>1500</v>
       </c>
       <c r="E17" s="3">
         <v>1600</v>
@@ -1397,8 +1397,8 @@
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>3</v>
+      <c r="D23" s="3">
+        <v>-1600</v>
       </c>
       <c r="E23" s="3">
         <v>-1700</v>
@@ -1547,8 +1547,8 @@
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>3</v>
+      <c r="D26" s="3">
+        <v>-1600</v>
       </c>
       <c r="E26" s="3">
         <v>-1700</v>
@@ -1597,8 +1597,8 @@
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>3</v>
+      <c r="D27" s="3">
+        <v>-1600</v>
       </c>
       <c r="E27" s="3">
         <v>-1700</v>
@@ -1897,8 +1897,8 @@
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>3</v>
+      <c r="D33" s="3">
+        <v>-1600</v>
       </c>
       <c r="E33" s="3">
         <v>-1700</v>
@@ -1997,8 +1997,8 @@
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>3</v>
+      <c r="D35" s="3">
+        <v>-1600</v>
       </c>
       <c r="E35" s="3">
         <v>-1700</v>
@@ -2543,25 +2543,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>0</v>
-      </c>
-      <c r="E49" s="3">
-        <v>0</v>
-      </c>
-      <c r="F49" s="3">
-        <v>0</v>
-      </c>
-      <c r="G49" s="3">
-        <v>0</v>
-      </c>
-      <c r="H49" s="3">
-        <v>0</v>
-      </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
-      <c r="J49" s="3">
-        <v>0</v>
+        <v>1600</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K49" s="3">
         <v>0</v>
@@ -3802,8 +3802,8 @@
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3" t="s">
-        <v>3</v>
+      <c r="D76" s="3">
+        <v>8600</v>
       </c>
       <c r="E76" s="3">
         <v>-1700</v>
@@ -3957,8 +3957,8 @@
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>3</v>
+      <c r="D81" s="3">
+        <v>-1600</v>
       </c>
       <c r="E81" s="3">
         <v>-1700</v>

--- a/AAII_Financials/Quarterly/HSCS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HSCS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="92">
   <si>
     <t>HSCS</t>
   </si>
@@ -656,87 +656,94 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45504</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45412</v>
+      </c>
+      <c r="F7" s="2">
         <v>45322</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45230</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45138</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45046</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44957</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44865</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44773</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44681</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44592</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44500</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44408</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44316</v>
       </c>
-      <c r="P7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="T7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -785,25 +792,31 @@
       <c r="R8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3">
+        <v>0</v>
+      </c>
+      <c r="T8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3">
-        <v>0</v>
-      </c>
-      <c r="E9" s="3">
-        <v>0</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H9" s="3">
-        <v>0</v>
+      <c r="D9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F9" s="3">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>3</v>
@@ -811,49 +824,55 @@
       <c r="J9" s="3">
         <v>0</v>
       </c>
-      <c r="K9" s="3">
-        <v>0</v>
+      <c r="K9" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L9" s="3">
         <v>0</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>3</v>
+      <c r="M9" s="3">
+        <v>0</v>
       </c>
       <c r="N9" s="3">
         <v>0</v>
       </c>
-      <c r="O9" s="3">
-        <v>0</v>
-      </c>
-      <c r="P9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q9" s="3" t="s">
-        <v>3</v>
+      <c r="O9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P9" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>0</v>
       </c>
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E10" s="3">
-        <v>0</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H10" s="3">
-        <v>0</v>
+      <c r="E10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>3</v>
@@ -861,32 +880,38 @@
       <c r="J10" s="3">
         <v>0</v>
       </c>
-      <c r="K10" s="3">
-        <v>0</v>
+      <c r="K10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L10" s="3">
         <v>0</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>3</v>
+      <c r="M10" s="3">
+        <v>0</v>
       </c>
       <c r="N10" s="3">
         <v>0</v>
       </c>
-      <c r="O10" s="3">
-        <v>0</v>
-      </c>
-      <c r="P10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q10" s="3" t="s">
-        <v>3</v>
+      <c r="O10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P10" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>0</v>
       </c>
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -905,58 +930,66 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E12" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F12" s="3">
         <v>500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>800</v>
-      </c>
-      <c r="F12" s="3">
-        <v>600</v>
-      </c>
-      <c r="G12" s="3">
-        <v>500</v>
       </c>
       <c r="H12" s="3">
         <v>600</v>
       </c>
       <c r="I12" s="3">
+        <v>500</v>
+      </c>
+      <c r="J12" s="3">
+        <v>600</v>
+      </c>
+      <c r="K12" s="3">
         <v>800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>1400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>1600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>600</v>
       </c>
-      <c r="P12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1005,8 +1038,14 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1019,11 +1058,11 @@
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I14" s="3">
         <v>0</v>
@@ -1035,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="L14" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1046,17 +1085,23 @@
       <c r="O14" s="3">
         <v>0</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
+      <c r="P14" s="3">
+        <v>-300</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>0</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1105,8 +1150,14 @@
       <c r="R15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1122,19 +1173,21 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E17" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F17" s="3">
         <v>1500</v>
-      </c>
-      <c r="E17" s="3">
-        <v>1600</v>
-      </c>
-      <c r="F17" s="3">
-        <v>1300</v>
       </c>
       <c r="G17" s="3">
         <v>1600</v>
@@ -1143,37 +1196,43 @@
         <v>1300</v>
       </c>
       <c r="I17" s="3">
+        <v>1600</v>
+      </c>
+      <c r="J17" s="3">
+        <v>1300</v>
+      </c>
+      <c r="K17" s="3">
         <v>1800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>1400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>2000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>2500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>1000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>800</v>
       </c>
-      <c r="P17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1181,10 +1240,10 @@
         <v>3</v>
       </c>
       <c r="E18" s="3">
-        <v>-1600</v>
+        <v>-1900</v>
       </c>
       <c r="F18" s="3">
-        <v>-1300</v>
+        <v>-1500</v>
       </c>
       <c r="G18" s="3">
         <v>-1600</v>
@@ -1193,37 +1252,43 @@
         <v>-1300</v>
       </c>
       <c r="I18" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="K18" s="3">
         <v>-1800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-1400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-2000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-2500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-1000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-800</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1242,8 +1307,10 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1251,7 +1318,7 @@
         <v>3</v>
       </c>
       <c r="E20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F20" s="3">
         <v>0</v>
@@ -1283,17 +1350,23 @@
       <c r="O20" s="3">
         <v>0</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>0</v>
       </c>
       <c r="R20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1301,10 +1374,10 @@
         <v>3</v>
       </c>
       <c r="E21" s="3">
-        <v>-1600</v>
+        <v>-1800</v>
       </c>
       <c r="F21" s="3">
-        <v>-1300</v>
+        <v>-1500</v>
       </c>
       <c r="G21" s="3">
         <v>-1600</v>
@@ -1313,52 +1386,58 @@
         <v>-1300</v>
       </c>
       <c r="I21" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="K21" s="3">
         <v>-1800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-1400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-2000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-2500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-1000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-800</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3">
         <v>100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>200</v>
       </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
       <c r="H22" s="3">
         <v>0</v>
       </c>
@@ -1366,84 +1445,96 @@
         <v>0</v>
       </c>
       <c r="J22" s="3">
+        <v>0</v>
+      </c>
+      <c r="K22" s="3">
+        <v>0</v>
+      </c>
+      <c r="L22" s="3">
         <v>100</v>
-      </c>
-      <c r="K22" s="3">
-        <v>100</v>
-      </c>
-      <c r="L22" s="3">
-        <v>300</v>
       </c>
       <c r="M22" s="3">
         <v>100</v>
       </c>
       <c r="N22" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="O22" s="3">
         <v>100</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q22" s="3" t="s">
-        <v>3</v>
+      <c r="P22" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>100</v>
       </c>
       <c r="R22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
+      <c r="D23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="F23" s="3">
         <v>-1600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-1700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-1400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-1600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-1300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-1800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-1600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-2100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-2800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-1000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-900</v>
       </c>
-      <c r="P23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1492,8 +1583,14 @@
       <c r="R24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1542,108 +1639,126 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
+      <c r="D26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="F26" s="3">
         <v>-1600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-1700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-1400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-1600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-1300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-1800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-1600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-2100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-2800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-1000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-900</v>
       </c>
-      <c r="P26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="F27" s="3">
         <v>-1600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-1700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-1400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-1600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-1300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-1800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-1600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-2100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-2800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-1000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-900</v>
       </c>
-      <c r="P27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1692,8 +1807,14 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1742,8 +1863,14 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1792,8 +1919,14 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1842,8 +1975,14 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1851,7 +1990,7 @@
         <v>3</v>
       </c>
       <c r="E32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F32" s="3">
         <v>0</v>
@@ -1883,67 +2022,79 @@
       <c r="O32" s="3">
         <v>0</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
+      <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>0</v>
       </c>
       <c r="R32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="F33" s="3">
         <v>-1600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-1700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-1400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-1600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-1300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-1800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-1600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-2100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-2800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-1000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-900</v>
       </c>
-      <c r="P33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1992,113 +2143,131 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="F35" s="3">
         <v>-1600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-1700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-1400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-1600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-1300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-1800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-1600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-2100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-2800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-1000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-900</v>
       </c>
-      <c r="P35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45504</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45412</v>
+      </c>
+      <c r="F38" s="2">
         <v>45322</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45230</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45138</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45046</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44957</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44865</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44773</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44681</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44592</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44500</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44408</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44316</v>
       </c>
-      <c r="P38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="T38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2117,8 +2286,10 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2137,44 +2308,46 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E41" s="3">
+        <v>5800</v>
+      </c>
+      <c r="F41" s="3">
         <v>7100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>1700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>1900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>3100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>4300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>1300</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2187,8 +2360,14 @@
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2237,25 +2416,31 @@
       <c r="R42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>0</v>
-      </c>
-      <c r="E43" s="3">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>3</v>
+      <c r="D43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F43" s="3">
+        <v>0</v>
       </c>
       <c r="G43" s="3">
         <v>0</v>
       </c>
-      <c r="H43" s="3">
-        <v>0</v>
+      <c r="H43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I43" s="3">
         <v>0</v>
@@ -2266,11 +2451,11 @@
       <c r="K43" s="3">
         <v>0</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M43" s="3" t="s">
-        <v>3</v>
+      <c r="L43" s="3">
+        <v>0</v>
+      </c>
+      <c r="M43" s="3">
+        <v>0</v>
       </c>
       <c r="N43" s="3" t="s">
         <v>3</v>
@@ -2287,16 +2472,22 @@
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="E44" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="F44" s="3">
         <v>700</v>
@@ -2319,11 +2510,11 @@
       <c r="L44" s="3">
         <v>700</v>
       </c>
-      <c r="M44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N44" s="3" t="s">
-        <v>3</v>
+      <c r="M44" s="3">
+        <v>700</v>
+      </c>
+      <c r="N44" s="3">
+        <v>700</v>
       </c>
       <c r="O44" s="3" t="s">
         <v>3</v>
@@ -2337,44 +2528,50 @@
       <c r="R44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E45" s="3">
         <v>900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
+        <v>900</v>
+      </c>
+      <c r="G45" s="3">
         <v>1000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>800</v>
-      </c>
-      <c r="G45" s="3">
-        <v>400</v>
-      </c>
-      <c r="H45" s="3">
-        <v>300</v>
       </c>
       <c r="I45" s="3">
         <v>400</v>
       </c>
       <c r="J45" s="3">
+        <v>300</v>
+      </c>
+      <c r="K45" s="3">
+        <v>400</v>
+      </c>
+      <c r="L45" s="3">
         <v>500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>400</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2387,44 +2584,50 @@
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E46" s="3">
+        <v>7400</v>
+      </c>
+      <c r="F46" s="3">
         <v>8700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>1800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>2000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>2700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>2900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>4100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>5400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>1900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>2400</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2437,8 +2640,14 @@
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2487,8 +2696,14 @@
       <c r="R47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3">
+        <v>0</v>
+      </c>
+      <c r="T47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2499,7 +2714,7 @@
         <v>600</v>
       </c>
       <c r="F48" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="G48" s="3">
         <v>600</v>
@@ -2511,20 +2726,20 @@
         <v>600</v>
       </c>
       <c r="J48" s="3">
+        <v>600</v>
+      </c>
+      <c r="K48" s="3">
+        <v>600</v>
+      </c>
+      <c r="L48" s="3">
         <v>100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>200</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2537,19 +2752,25 @@
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
         <v>1600</v>
       </c>
-      <c r="E49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>3</v>
+      <c r="E49" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F49" s="3">
+        <v>1600</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>3</v>
@@ -2563,11 +2784,11 @@
       <c r="J49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K49" s="3">
-        <v>0</v>
-      </c>
-      <c r="L49" s="3">
-        <v>0</v>
+      <c r="K49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M49" s="3">
         <v>0</v>
@@ -2587,8 +2808,14 @@
       <c r="R49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3">
+        <v>0</v>
+      </c>
+      <c r="T49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2637,8 +2864,14 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2687,8 +2920,14 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2737,8 +2976,14 @@
       <c r="R52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3">
+        <v>0</v>
+      </c>
+      <c r="T52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2787,44 +3032,50 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E54" s="3">
+        <v>9500</v>
+      </c>
+      <c r="F54" s="3">
         <v>10800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>2400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>2600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>3300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>3500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>4800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>5600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>2100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>2600</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2837,8 +3088,14 @@
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2857,8 +3114,10 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2877,8 +3136,10 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2886,35 +3147,35 @@
         <v>400</v>
       </c>
       <c r="E57" s="3">
+        <v>400</v>
+      </c>
+      <c r="F57" s="3">
+        <v>400</v>
+      </c>
+      <c r="G57" s="3">
         <v>1100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>1000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>400</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2927,44 +3188,50 @@
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3">
         <v>500</v>
-      </c>
-      <c r="E58" s="3">
-        <v>1400</v>
       </c>
       <c r="F58" s="3">
         <v>500</v>
       </c>
       <c r="G58" s="3">
+        <v>1400</v>
+      </c>
+      <c r="H58" s="3">
         <v>500</v>
       </c>
-      <c r="H58" s="3">
-        <v>100</v>
-      </c>
       <c r="I58" s="3">
-        <v>1100</v>
+        <v>500</v>
       </c>
       <c r="J58" s="3">
         <v>100</v>
       </c>
       <c r="K58" s="3">
+        <v>1100</v>
+      </c>
+      <c r="L58" s="3">
+        <v>100</v>
+      </c>
+      <c r="M58" s="3">
         <v>1600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>2600</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2977,43 +3244,49 @@
       <c r="R58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E59" s="3">
         <v>800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
+        <v>800</v>
+      </c>
+      <c r="G59" s="3">
         <v>1000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>1200</v>
-      </c>
-      <c r="J59" s="3">
-        <v>1000</v>
-      </c>
-      <c r="K59" s="3">
-        <v>1100</v>
       </c>
       <c r="L59" s="3">
         <v>1000</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
+      <c r="M59" s="3">
+        <v>1100</v>
+      </c>
+      <c r="N59" s="3">
+        <v>1000</v>
       </c>
       <c r="O59" s="3" t="s">
         <v>3</v>
@@ -3027,44 +3300,50 @@
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E60" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F60" s="3">
         <v>1700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>3500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>1900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>1800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>2000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>3100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>1500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>3500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>4100</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3077,44 +3356,50 @@
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E61" s="3">
         <v>0</v>
       </c>
       <c r="F61" s="3">
+        <v>0</v>
+      </c>
+      <c r="G61" s="3">
+        <v>0</v>
+      </c>
+      <c r="H61" s="3">
         <v>500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>500</v>
-      </c>
-      <c r="H61" s="3">
-        <v>1000</v>
-      </c>
-      <c r="I61" s="3">
-        <v>0</v>
       </c>
       <c r="J61" s="3">
         <v>1000</v>
       </c>
       <c r="K61" s="3">
+        <v>0</v>
+      </c>
+      <c r="L61" s="3">
+        <v>1000</v>
+      </c>
+      <c r="M61" s="3">
         <v>4400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>2600</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
@@ -3127,43 +3412,49 @@
       <c r="R61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>400</v>
+      </c>
+      <c r="E62" s="3">
+        <v>400</v>
+      </c>
+      <c r="F62" s="3">
         <v>500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>200</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
-      </c>
-      <c r="M62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N62" s="3" t="s">
-        <v>3</v>
+      <c r="N62" s="3">
+        <v>0</v>
       </c>
       <c r="O62" s="3" t="s">
         <v>3</v>
@@ -3177,8 +3468,14 @@
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3227,8 +3524,14 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3277,8 +3580,14 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3327,44 +3636,50 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E66" s="3">
         <v>2200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
+        <v>2200</v>
+      </c>
+      <c r="G66" s="3">
         <v>4000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>3100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>3100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>3700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>3700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>2700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>8100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>6700</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3377,8 +3692,14 @@
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3397,8 +3718,10 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3447,8 +3770,14 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3497,8 +3826,14 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3547,8 +3882,14 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3597,44 +3938,50 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-69400</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-67400</v>
+      </c>
+      <c r="F72" s="3">
         <v>-65500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-63900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-62100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-60800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-59100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-57800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-56000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-54400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-52300</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3647,8 +3994,14 @@
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3697,8 +4050,14 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3747,8 +4106,14 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3797,44 +4162,50 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3">
+      <c r="D76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E76" s="3">
+        <v>7300</v>
+      </c>
+      <c r="F76" s="3">
         <v>8600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>-1700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>-500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>-300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>1100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>2900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>-6100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>-4100</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3847,8 +4218,14 @@
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3897,113 +4274,131 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45504</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45412</v>
+      </c>
+      <c r="F80" s="2">
         <v>45322</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45230</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45138</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45046</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44957</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44865</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44773</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44681</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44592</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44500</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44408</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44316</v>
       </c>
-      <c r="P80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="T80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="F81" s="3">
         <v>-1600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-1700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-1400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-1600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-1300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-1800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-1600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-2100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-2800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-1000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-900</v>
       </c>
-      <c r="P81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4022,8 +4417,10 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4063,17 +4460,23 @@
       <c r="O83" s="3">
         <v>0</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q83" s="3" t="s">
-        <v>3</v>
+      <c r="P83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="3">
+        <v>0</v>
       </c>
       <c r="R83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4122,8 +4525,14 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4172,8 +4581,14 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4222,8 +4637,14 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4272,8 +4693,14 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4322,58 +4749,70 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="F89" s="3">
         <v>-2100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-1000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-1400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-1900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-1000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-1100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-1800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-1200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-2500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-700</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4392,8 +4831,10 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4401,7 +4842,7 @@
         <v>0</v>
       </c>
       <c r="E91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F91" s="3">
         <v>0</v>
@@ -4430,11 +4871,11 @@
       <c r="N91" s="3">
         <v>0</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P91" s="3" t="s">
-        <v>3</v>
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
+        <v>0</v>
       </c>
       <c r="Q91" s="3" t="s">
         <v>3</v>
@@ -4442,8 +4883,14 @@
       <c r="R91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4492,8 +4939,14 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4542,8 +4995,14 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -4551,7 +5010,7 @@
         <v>0</v>
       </c>
       <c r="E94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F94" s="3">
         <v>0</v>
@@ -4583,17 +5042,23 @@
       <c r="O94" s="3">
         <v>0</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
+      <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
+        <v>0</v>
       </c>
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4612,8 +5077,10 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4662,8 +5129,14 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4712,8 +5185,14 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4762,8 +5241,14 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4812,58 +5297,70 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>600</v>
+      </c>
+      <c r="E100" s="3">
+        <v>400</v>
+      </c>
+      <c r="F100" s="3">
         <v>9100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>1600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>5200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>3100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>1100</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>500</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4912,54 +5409,66 @@
       <c r="R101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="F102" s="3">
         <v>7000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-500</v>
-      </c>
-      <c r="F102" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="G102" s="3">
-        <v>-300</v>
       </c>
       <c r="H102" s="3">
         <v>-1100</v>
       </c>
       <c r="I102" s="3">
+        <v>-300</v>
+      </c>
+      <c r="J102" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="K102" s="3">
         <v>-1200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>3400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-200</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/HSCS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HSCS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="92">
   <si>
     <t>HSCS</t>
   </si>
@@ -759,8 +759,8 @@
       <c r="G8" s="3">
         <v>0</v>
       </c>
-      <c r="H8" s="3">
-        <v>0</v>
+      <c r="H8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I8" s="3">
         <v>0</v>
@@ -806,8 +806,8 @@
       <c r="D9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>3</v>
+      <c r="E9" s="3">
+        <v>0</v>
       </c>
       <c r="F9" s="3">
         <v>0</v>
@@ -818,8 +818,8 @@
       <c r="H9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I9" s="3" t="s">
-        <v>3</v>
+      <c r="I9" s="3">
+        <v>0</v>
       </c>
       <c r="J9" s="3">
         <v>0</v>
@@ -862,8 +862,8 @@
       <c r="D10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>3</v>
+      <c r="E10" s="3">
+        <v>0</v>
       </c>
       <c r="F10" s="3">
         <v>0</v>
@@ -874,8 +874,8 @@
       <c r="H10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
+      <c r="I10" s="3">
+        <v>0</v>
       </c>
       <c r="J10" s="3">
         <v>0</v>
@@ -1064,11 +1064,11 @@
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1236,8 +1236,8 @@
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>3</v>
+      <c r="D18" s="3">
+        <v>-2100</v>
       </c>
       <c r="E18" s="3">
         <v>-1900</v>
@@ -1314,11 +1314,11 @@
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
+      <c r="D20" s="3">
+        <v>0</v>
       </c>
       <c r="E20" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="F20" s="3">
         <v>0</v>
@@ -1370,8 +1370,8 @@
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>3</v>
+      <c r="D21" s="3">
+        <v>-2000</v>
       </c>
       <c r="E21" s="3">
         <v>-1800</v>
@@ -1482,8 +1482,8 @@
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>3</v>
+      <c r="D23" s="3">
+        <v>-2100</v>
       </c>
       <c r="E23" s="3">
         <v>-1800</v>
@@ -1538,26 +1538,26 @@
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -1650,8 +1650,8 @@
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>3</v>
+      <c r="D26" s="3">
+        <v>-2100</v>
       </c>
       <c r="E26" s="3">
         <v>-1800</v>
@@ -1706,8 +1706,8 @@
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>3</v>
+      <c r="D27" s="3">
+        <v>-2100</v>
       </c>
       <c r="E27" s="3">
         <v>-1800</v>
@@ -1986,11 +1986,11 @@
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
+      <c r="D32" s="3">
+        <v>0</v>
       </c>
       <c r="E32" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="F32" s="3">
         <v>0</v>
@@ -2042,8 +2042,8 @@
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>3</v>
+      <c r="D33" s="3">
+        <v>-2100</v>
       </c>
       <c r="E33" s="3">
         <v>-1800</v>
@@ -2154,8 +2154,8 @@
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>3</v>
+      <c r="D35" s="3">
+        <v>-2100</v>
       </c>
       <c r="E35" s="3">
         <v>-1800</v>
@@ -2442,11 +2442,11 @@
       <c r="H43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0</v>
+      <c r="I43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -2540,25 +2540,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1100</v>
+        <v>700</v>
       </c>
       <c r="E45" s="3">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="F45" s="3">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="G45" s="3">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="H45" s="3">
-        <v>800</v>
+        <v>300</v>
       </c>
       <c r="I45" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="J45" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="K45" s="3">
         <v>400</v>
@@ -2651,26 +2651,26 @@
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2772,17 +2772,17 @@
       <c r="F49" s="3">
         <v>1600</v>
       </c>
-      <c r="G49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>3</v>
+      <c r="G49" s="3">
+        <v>0</v>
+      </c>
+      <c r="H49" s="3">
+        <v>0</v>
+      </c>
+      <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3">
+        <v>0</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>3</v>
@@ -2931,26 +2931,26 @@
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>0</v>
-      </c>
-      <c r="E52" s="3">
-        <v>0</v>
-      </c>
-      <c r="F52" s="3">
-        <v>0</v>
-      </c>
-      <c r="G52" s="3">
-        <v>0</v>
-      </c>
-      <c r="H52" s="3">
-        <v>0</v>
-      </c>
-      <c r="I52" s="3">
-        <v>0</v>
-      </c>
-      <c r="J52" s="3">
-        <v>0</v>
+      <c r="D52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -3200,19 +3200,19 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E58" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="F58" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="G58" s="3">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="H58" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="I58" s="3">
         <v>500</v>
@@ -3256,25 +3256,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="E59" s="3">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="F59" s="3">
-        <v>800</v>
+        <v>100</v>
       </c>
       <c r="G59" s="3">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="H59" s="3">
-        <v>900</v>
+        <v>200</v>
       </c>
       <c r="I59" s="3">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="J59" s="3">
-        <v>800</v>
+        <v>200</v>
       </c>
       <c r="K59" s="3">
         <v>1200</v>
@@ -3368,25 +3368,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>900</v>
+      </c>
+      <c r="E61" s="3">
+        <v>400</v>
+      </c>
+      <c r="F61" s="3">
         <v>500</v>
       </c>
-      <c r="E61" s="3">
-        <v>0</v>
-      </c>
-      <c r="F61" s="3">
-        <v>0</v>
-      </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="H61" s="3">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="I61" s="3">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="J61" s="3">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -3423,26 +3423,26 @@
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>400</v>
-      </c>
-      <c r="E62" s="3">
-        <v>400</v>
-      </c>
-      <c r="F62" s="3">
-        <v>500</v>
-      </c>
-      <c r="G62" s="3">
-        <v>500</v>
+      <c r="D62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H62" s="3">
-        <v>700</v>
+        <v>200</v>
       </c>
       <c r="I62" s="3">
-        <v>700</v>
+        <v>200</v>
       </c>
       <c r="J62" s="3">
-        <v>800</v>
+        <v>200</v>
       </c>
       <c r="K62" s="3">
         <v>500</v>
@@ -4173,8 +4173,8 @@
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3" t="s">
-        <v>3</v>
+      <c r="D76" s="3">
+        <v>5900</v>
       </c>
       <c r="E76" s="3">
         <v>7300</v>
@@ -4346,8 +4346,8 @@
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>3</v>
+      <c r="D81" s="3">
+        <v>-2100</v>
       </c>
       <c r="E81" s="3">
         <v>-1800</v>
@@ -4428,7 +4428,7 @@
         <v>0</v>
       </c>
       <c r="E83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F83" s="3">
         <v>0</v>
@@ -4838,11 +4838,11 @@
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F91" s="3">
         <v>0</v>
@@ -4850,8 +4850,8 @@
       <c r="G91" s="3">
         <v>0</v>
       </c>
-      <c r="H91" s="3">
-        <v>0</v>
+      <c r="H91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I91" s="3">
         <v>0</v>
@@ -5084,26 +5084,26 @@
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -5364,26 +5364,26 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>

--- a/AAII_Financials/Quarterly/HSCS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HSCS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="92">
   <si>
     <t>HSCS</t>
   </si>
@@ -656,117 +656,125 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45688</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45596</v>
+      </c>
+      <c r="F7" s="2">
         <v>45504</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45412</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45322</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45230</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45138</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45046</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44957</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44865</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44773</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44681</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44592</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44500</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44408</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44316</v>
       </c>
-      <c r="R7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="S7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="V7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E8" s="3">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3">
-        <v>0</v>
+      <c r="E8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G8" s="3">
         <v>0</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>3</v>
+      <c r="H8" s="3">
+        <v>0</v>
       </c>
       <c r="I8" s="3">
         <v>0</v>
       </c>
-      <c r="J8" s="3">
-        <v>0</v>
+      <c r="J8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
@@ -798,120 +806,138 @@
       <c r="T8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U8" s="3">
+        <v>0</v>
+      </c>
+      <c r="V8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E9" s="3">
-        <v>0</v>
-      </c>
-      <c r="F9" s="3">
-        <v>0</v>
+      <c r="E9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G9" s="3">
         <v>0</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>3</v>
+      <c r="H9" s="3">
+        <v>0</v>
       </c>
       <c r="I9" s="3">
         <v>0</v>
       </c>
-      <c r="J9" s="3">
-        <v>0</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>3</v>
+      <c r="J9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K9" s="3">
+        <v>0</v>
       </c>
       <c r="L9" s="3">
         <v>0</v>
       </c>
-      <c r="M9" s="3">
-        <v>0</v>
+      <c r="M9" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N9" s="3">
         <v>0</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>3</v>
+      <c r="O9" s="3">
+        <v>0</v>
       </c>
       <c r="P9" s="3">
         <v>0</v>
       </c>
-      <c r="Q9" s="3">
-        <v>0</v>
-      </c>
-      <c r="R9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S9" s="3" t="s">
-        <v>3</v>
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R9" s="3">
+        <v>0</v>
+      </c>
+      <c r="S9" s="3">
+        <v>0</v>
       </c>
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E10" s="3">
-        <v>0</v>
-      </c>
-      <c r="F10" s="3">
-        <v>0</v>
+      <c r="E10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G10" s="3">
         <v>0</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
+      <c r="H10" s="3">
+        <v>0</v>
       </c>
       <c r="I10" s="3">
         <v>0</v>
       </c>
-      <c r="J10" s="3">
-        <v>0</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
+      <c r="J10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K10" s="3">
+        <v>0</v>
       </c>
       <c r="L10" s="3">
         <v>0</v>
       </c>
-      <c r="M10" s="3">
-        <v>0</v>
+      <c r="M10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N10" s="3">
         <v>0</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>3</v>
+      <c r="O10" s="3">
+        <v>0</v>
       </c>
       <c r="P10" s="3">
         <v>0</v>
       </c>
-      <c r="Q10" s="3">
-        <v>0</v>
-      </c>
-      <c r="R10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S10" s="3" t="s">
-        <v>3</v>
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R10" s="3">
+        <v>0</v>
+      </c>
+      <c r="S10" s="3">
+        <v>0</v>
       </c>
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -932,64 +958,72 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E12" s="3">
         <v>1200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
+        <v>1200</v>
+      </c>
+      <c r="G12" s="3">
         <v>1000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>800</v>
-      </c>
-      <c r="H12" s="3">
-        <v>600</v>
-      </c>
-      <c r="I12" s="3">
-        <v>500</v>
       </c>
       <c r="J12" s="3">
         <v>600</v>
       </c>
       <c r="K12" s="3">
+        <v>500</v>
+      </c>
+      <c r="L12" s="3">
+        <v>600</v>
+      </c>
+      <c r="M12" s="3">
         <v>800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>1400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>1600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>600</v>
       </c>
-      <c r="R12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1044,8 +1078,14 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1070,17 +1110,17 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
       <c r="N14" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
@@ -1091,17 +1131,23 @@
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>3</v>
+      <c r="R14" s="3">
+        <v>-300</v>
+      </c>
+      <c r="S14" s="3">
+        <v>0</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1156,8 +1202,14 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1175,25 +1227,27 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E17" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F17" s="3">
         <v>2100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>1900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>1500</v>
-      </c>
-      <c r="G17" s="3">
-        <v>1600</v>
-      </c>
-      <c r="H17" s="3">
-        <v>1300</v>
       </c>
       <c r="I17" s="3">
         <v>1600</v>
@@ -1202,54 +1256,60 @@
         <v>1300</v>
       </c>
       <c r="K17" s="3">
+        <v>1600</v>
+      </c>
+      <c r="L17" s="3">
+        <v>1300</v>
+      </c>
+      <c r="M17" s="3">
         <v>1800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>1400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>2000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>2500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>1000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>800</v>
       </c>
-      <c r="R17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="F18" s="3">
         <v>-2100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-1900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-1500</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-1300</v>
       </c>
       <c r="I18" s="3">
         <v>-1600</v>
@@ -1258,37 +1318,43 @@
         <v>-1300</v>
       </c>
       <c r="K18" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="L18" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="M18" s="3">
         <v>-1800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-1400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-2000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-2500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-1000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-800</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1309,8 +1375,10 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1318,14 +1386,14 @@
         <v>0</v>
       </c>
       <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
         <v>-100</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
       <c r="H20" s="3">
         <v>0</v>
       </c>
@@ -1356,34 +1424,40 @@
       <c r="Q20" s="3">
         <v>0</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
+      <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
+        <v>0</v>
       </c>
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E21" s="3">
         <v>-2000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="G21" s="3">
         <v>-1800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-1500</v>
-      </c>
-      <c r="G21" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="H21" s="3">
-        <v>-1300</v>
       </c>
       <c r="I21" s="3">
         <v>-1600</v>
@@ -1392,58 +1466,64 @@
         <v>-1300</v>
       </c>
       <c r="K21" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="L21" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="M21" s="3">
         <v>-1800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-1400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-2000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-2500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-1000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-800</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F22" s="3">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3">
         <v>100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>200</v>
       </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
       <c r="J22" s="3">
         <v>0</v>
       </c>
@@ -1451,90 +1531,102 @@
         <v>0</v>
       </c>
       <c r="L22" s="3">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3">
         <v>100</v>
-      </c>
-      <c r="M22" s="3">
-        <v>100</v>
-      </c>
-      <c r="N22" s="3">
-        <v>300</v>
       </c>
       <c r="O22" s="3">
         <v>100</v>
       </c>
       <c r="P22" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="Q22" s="3">
         <v>100</v>
       </c>
-      <c r="R22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S22" s="3" t="s">
-        <v>3</v>
+      <c r="R22" s="3">
+        <v>100</v>
+      </c>
+      <c r="S22" s="3">
+        <v>100</v>
       </c>
       <c r="T22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-2100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="G23" s="3">
         <v>-1800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-1600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-1700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-1400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-1600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-1300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-1800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-1600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-2100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-2800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-1000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-900</v>
       </c>
-      <c r="R23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1559,11 +1651,11 @@
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -1589,8 +1681,14 @@
       <c r="T24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U24" s="3">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1645,120 +1743,138 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-2100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="G26" s="3">
         <v>-1800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-1600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-1700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-1400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-1600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-1300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-1800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-1600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-2100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-2800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-1000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-900</v>
       </c>
-      <c r="R26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-2100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="G27" s="3">
         <v>-1800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-1600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-1700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-1400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-1600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-1300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-1800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-1600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-2100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-2800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-1000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-900</v>
       </c>
-      <c r="R27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1813,8 +1929,14 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1869,8 +1991,14 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1925,8 +2053,14 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1981,8 +2115,14 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1990,14 +2130,14 @@
         <v>0</v>
       </c>
       <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
         <v>100</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
       <c r="H32" s="3">
         <v>0</v>
       </c>
@@ -2028,73 +2168,85 @@
       <c r="Q32" s="3">
         <v>0</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
+      <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
+        <v>0</v>
       </c>
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-2100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="G33" s="3">
         <v>-1800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-1600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-1700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-1400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-1600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-1300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-1800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-1600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-2100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-2800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-1000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-900</v>
       </c>
-      <c r="R33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2149,125 +2301,143 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-2100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="G35" s="3">
         <v>-1800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-1600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-1700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-1400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-1600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-1300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-1800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-1600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-2100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-2800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-1000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-900</v>
       </c>
-      <c r="R35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45688</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45596</v>
+      </c>
+      <c r="F38" s="2">
         <v>45504</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45412</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45322</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45230</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45138</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45046</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44957</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44865</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44773</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44681</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44592</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44500</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44408</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44316</v>
       </c>
-      <c r="R38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="S38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="V38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2288,8 +2458,10 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2310,50 +2482,52 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E41" s="3">
+        <v>4100</v>
+      </c>
+      <c r="F41" s="3">
         <v>4300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>5800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>7100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>1700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>1900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>3100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>4300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>1300</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2366,8 +2540,14 @@
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2422,8 +2602,14 @@
       <c r="T42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2433,35 +2619,35 @@
       <c r="E43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F43" s="3">
-        <v>0</v>
-      </c>
-      <c r="G43" s="3">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
+      <c r="F43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H43" s="3">
+        <v>0</v>
+      </c>
+      <c r="I43" s="3">
+        <v>0</v>
       </c>
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
-      </c>
-      <c r="L43" s="3">
-        <v>0</v>
+      <c r="K43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M43" s="3">
         <v>0</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O43" s="3" t="s">
-        <v>3</v>
+      <c r="N43" s="3">
+        <v>0</v>
+      </c>
+      <c r="O43" s="3">
+        <v>0</v>
       </c>
       <c r="P43" s="3" t="s">
         <v>3</v>
@@ -2478,22 +2664,28 @@
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>700</v>
+      </c>
+      <c r="E44" s="3">
+        <v>700</v>
+      </c>
+      <c r="F44" s="3">
         <v>600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>600</v>
-      </c>
-      <c r="F44" s="3">
-        <v>700</v>
-      </c>
-      <c r="G44" s="3">
-        <v>700</v>
       </c>
       <c r="H44" s="3">
         <v>700</v>
@@ -2516,11 +2708,11 @@
       <c r="N44" s="3">
         <v>700</v>
       </c>
-      <c r="O44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P44" s="3" t="s">
-        <v>3</v>
+      <c r="O44" s="3">
+        <v>700</v>
+      </c>
+      <c r="P44" s="3">
+        <v>700</v>
       </c>
       <c r="Q44" s="3" t="s">
         <v>3</v>
@@ -2534,13 +2726,19 @@
       <c r="T44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>700</v>
+        <v>200</v>
       </c>
       <c r="E45" s="3">
         <v>700</v>
@@ -2552,32 +2750,32 @@
         <v>700</v>
       </c>
       <c r="H45" s="3">
+        <v>700</v>
+      </c>
+      <c r="I45" s="3">
+        <v>700</v>
+      </c>
+      <c r="J45" s="3">
         <v>300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>200</v>
       </c>
-      <c r="J45" s="3">
-        <v>0</v>
-      </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
+        <v>0</v>
+      </c>
+      <c r="M45" s="3">
         <v>400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>400</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2590,50 +2788,56 @@
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E46" s="3">
+        <v>5700</v>
+      </c>
+      <c r="F46" s="3">
         <v>6100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>7400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>8700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>1800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>2000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>2700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>2900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>4100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>5400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>1900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>2400</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2646,8 +2850,14 @@
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2672,11 +2882,11 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -2702,8 +2912,14 @@
       <c r="T47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3">
+        <v>0</v>
+      </c>
+      <c r="V47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2711,7 +2927,7 @@
         <v>500</v>
       </c>
       <c r="E48" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="F48" s="3">
         <v>500</v>
@@ -2720,7 +2936,7 @@
         <v>600</v>
       </c>
       <c r="H48" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="I48" s="3">
         <v>600</v>
@@ -2732,20 +2948,20 @@
         <v>600</v>
       </c>
       <c r="L48" s="3">
+        <v>600</v>
+      </c>
+      <c r="M48" s="3">
+        <v>600</v>
+      </c>
+      <c r="N48" s="3">
         <v>100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>200</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2758,8 +2974,14 @@
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2773,10 +2995,10 @@
         <v>1600</v>
       </c>
       <c r="G49" s="3">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="H49" s="3">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="I49" s="3">
         <v>0</v>
@@ -2784,17 +3006,17 @@
       <c r="J49" s="3">
         <v>0</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M49" s="3">
-        <v>0</v>
-      </c>
-      <c r="N49" s="3">
-        <v>0</v>
+      <c r="K49" s="3">
+        <v>0</v>
+      </c>
+      <c r="L49" s="3">
+        <v>0</v>
+      </c>
+      <c r="M49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O49" s="3">
         <v>0</v>
@@ -2814,8 +3036,14 @@
       <c r="T49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3">
+        <v>0</v>
+      </c>
+      <c r="V49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2870,8 +3098,14 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2926,8 +3160,14 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2952,11 +3192,11 @@
       <c r="J52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
-      </c>
-      <c r="L52" s="3">
-        <v>0</v>
+      <c r="K52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M52" s="3">
         <v>0</v>
@@ -2982,8 +3222,14 @@
       <c r="T52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3">
+        <v>0</v>
+      </c>
+      <c r="V52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3038,50 +3284,56 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E54" s="3">
+        <v>7800</v>
+      </c>
+      <c r="F54" s="3">
         <v>8200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>9500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>10800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>2400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>2600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>3300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>3500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>4800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>5600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>2100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>2600</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3094,8 +3346,14 @@
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3116,8 +3374,10 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3138,8 +3398,10 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3147,41 +3409,41 @@
         <v>400</v>
       </c>
       <c r="E57" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="F57" s="3">
         <v>400</v>
       </c>
       <c r="G57" s="3">
+        <v>400</v>
+      </c>
+      <c r="H57" s="3">
+        <v>400</v>
+      </c>
+      <c r="I57" s="3">
         <v>1100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>1000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>400</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3194,50 +3456,56 @@
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E58" s="3">
+        <v>2500</v>
+      </c>
+      <c r="F58" s="3">
         <v>100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>600</v>
-      </c>
-      <c r="F58" s="3">
-        <v>600</v>
-      </c>
-      <c r="G58" s="3">
-        <v>1500</v>
       </c>
       <c r="H58" s="3">
         <v>600</v>
       </c>
       <c r="I58" s="3">
+        <v>1500</v>
+      </c>
+      <c r="J58" s="3">
+        <v>600</v>
+      </c>
+      <c r="K58" s="3">
         <v>500</v>
-      </c>
-      <c r="J58" s="3">
-        <v>100</v>
-      </c>
-      <c r="K58" s="3">
-        <v>1100</v>
       </c>
       <c r="L58" s="3">
         <v>100</v>
       </c>
       <c r="M58" s="3">
+        <v>1100</v>
+      </c>
+      <c r="N58" s="3">
+        <v>100</v>
+      </c>
+      <c r="O58" s="3">
         <v>1600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>2600</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3250,49 +3518,55 @@
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>100</v>
+      </c>
+      <c r="E59" s="3">
         <v>200</v>
       </c>
-      <c r="E59" s="3">
-        <v>0</v>
-      </c>
       <c r="F59" s="3">
+        <v>200</v>
+      </c>
+      <c r="G59" s="3">
+        <v>0</v>
+      </c>
+      <c r="H59" s="3">
         <v>100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>200</v>
-      </c>
-      <c r="H59" s="3">
-        <v>200</v>
-      </c>
-      <c r="I59" s="3">
-        <v>0</v>
       </c>
       <c r="J59" s="3">
         <v>200</v>
       </c>
       <c r="K59" s="3">
+        <v>0</v>
+      </c>
+      <c r="L59" s="3">
+        <v>200</v>
+      </c>
+      <c r="M59" s="3">
         <v>1200</v>
-      </c>
-      <c r="L59" s="3">
-        <v>1000</v>
-      </c>
-      <c r="M59" s="3">
-        <v>1100</v>
       </c>
       <c r="N59" s="3">
         <v>1000</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P59" s="3" t="s">
-        <v>3</v>
+      <c r="O59" s="3">
+        <v>1100</v>
+      </c>
+      <c r="P59" s="3">
+        <v>1000</v>
       </c>
       <c r="Q59" s="3" t="s">
         <v>3</v>
@@ -3306,50 +3580,56 @@
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E60" s="3">
+        <v>3300</v>
+      </c>
+      <c r="F60" s="3">
         <v>1400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>1800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>1700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>3500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>1900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>1800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>2000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>3100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>1500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>3500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>4100</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3362,50 +3642,56 @@
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>900</v>
+        <v>300</v>
       </c>
       <c r="E61" s="3">
         <v>400</v>
       </c>
       <c r="F61" s="3">
+        <v>900</v>
+      </c>
+      <c r="G61" s="3">
+        <v>400</v>
+      </c>
+      <c r="H61" s="3">
         <v>500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>1000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>1000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>1500</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3">
         <v>1000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>4400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>2600</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -3418,16 +3704,22 @@
       <c r="T61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E62" s="3" t="s">
-        <v>3</v>
+      <c r="E62" s="3">
+        <v>0</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>3</v>
@@ -3435,32 +3727,32 @@
       <c r="G62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H62" s="3">
-        <v>200</v>
-      </c>
-      <c r="I62" s="3">
-        <v>200</v>
+      <c r="H62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J62" s="3">
         <v>200</v>
       </c>
       <c r="K62" s="3">
+        <v>200</v>
+      </c>
+      <c r="L62" s="3">
+        <v>200</v>
+      </c>
+      <c r="M62" s="3">
         <v>500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>200</v>
       </c>
-      <c r="N62" s="3">
-        <v>0</v>
-      </c>
-      <c r="O62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P62" s="3" t="s">
-        <v>3</v>
+      <c r="P62" s="3">
+        <v>0</v>
       </c>
       <c r="Q62" s="3" t="s">
         <v>3</v>
@@ -3474,8 +3766,14 @@
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3530,8 +3828,14 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3586,8 +3890,14 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3642,50 +3952,56 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E66" s="3">
+        <v>3800</v>
+      </c>
+      <c r="F66" s="3">
         <v>2300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>2200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>2200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>4000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>3100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>3100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>3700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>3700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>2700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>8100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>6700</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3698,8 +4014,14 @@
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3720,8 +4042,10 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3776,8 +4100,14 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3832,8 +4162,14 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3888,8 +4224,14 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3944,50 +4286,56 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-74000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-71500</v>
+      </c>
+      <c r="F72" s="3">
         <v>-69400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-67400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-65500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-63900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-62100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-60800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-59100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-57800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-56000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-54400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-52300</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4000,8 +4348,14 @@
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4056,8 +4410,14 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4112,8 +4472,14 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4168,50 +4534,56 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E76" s="3">
+        <v>4000</v>
+      </c>
+      <c r="F76" s="3">
         <v>5900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>7300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>8600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>-1700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>-500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>-300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>1100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>2900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>-6100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>-4100</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4224,8 +4596,14 @@
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4280,125 +4658,143 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45688</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45596</v>
+      </c>
+      <c r="F80" s="2">
         <v>45504</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45412</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45322</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45230</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45138</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45046</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44957</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44865</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44773</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44681</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44592</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44500</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44408</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44316</v>
       </c>
-      <c r="R80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="S80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="V80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-2100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="G81" s="3">
         <v>-1800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-1600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-1700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-1400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-1600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-1300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-1800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-1600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-2100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-2800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-1000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-900</v>
       </c>
-      <c r="R81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4419,8 +4815,10 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4428,14 +4826,14 @@
         <v>0</v>
       </c>
       <c r="E83" s="3">
+        <v>0</v>
+      </c>
+      <c r="F83" s="3">
+        <v>0</v>
+      </c>
+      <c r="G83" s="3">
         <v>100</v>
       </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
-      <c r="G83" s="3">
-        <v>0</v>
-      </c>
       <c r="H83" s="3">
         <v>0</v>
       </c>
@@ -4466,17 +4864,23 @@
       <c r="Q83" s="3">
         <v>0</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S83" s="3" t="s">
-        <v>3</v>
+      <c r="R83" s="3">
+        <v>0</v>
+      </c>
+      <c r="S83" s="3">
+        <v>0</v>
       </c>
       <c r="T83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4531,8 +4935,14 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4587,8 +4997,14 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4643,8 +5059,14 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4699,8 +5121,14 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4755,64 +5183,76 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="F89" s="3">
         <v>-2000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-1500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-2100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-1000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-1400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-1900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-1000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-1100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-1800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-1200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-2500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-700</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4833,31 +5273,33 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>3</v>
+      <c r="D91" s="3">
+        <v>0</v>
       </c>
       <c r="E91" s="3">
         <v>0</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
+      <c r="F91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G91" s="3">
         <v>0</v>
       </c>
-      <c r="H91" s="3" t="s">
-        <v>3</v>
+      <c r="H91" s="3">
+        <v>0</v>
       </c>
       <c r="I91" s="3">
         <v>0</v>
       </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="J91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -4877,11 +5319,11 @@
       <c r="P91" s="3">
         <v>0</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R91" s="3" t="s">
-        <v>3</v>
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
+        <v>0</v>
       </c>
       <c r="S91" s="3" t="s">
         <v>3</v>
@@ -4889,8 +5331,14 @@
       <c r="T91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4945,8 +5393,14 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5001,8 +5455,14 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5010,14 +5470,14 @@
         <v>0</v>
       </c>
       <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
         <v>-100</v>
       </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
       <c r="H94" s="3">
         <v>0</v>
       </c>
@@ -5048,17 +5508,23 @@
       <c r="Q94" s="3">
         <v>0</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S94" s="3" t="s">
-        <v>3</v>
+      <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3">
+        <v>0</v>
       </c>
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5079,8 +5545,10 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5105,11 +5573,11 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -5135,8 +5603,14 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5191,8 +5665,14 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5247,8 +5727,14 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5303,64 +5789,76 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>200</v>
+      </c>
+      <c r="E100" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F100" s="3">
         <v>600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>9100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>1600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>5200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>3100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>1100</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>500</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5385,11 +5883,11 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -5415,8 +5913,14 @@
       <c r="T101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -5424,51 +5928,57 @@
         <v>-1500</v>
       </c>
       <c r="E102" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F102" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="G102" s="3">
         <v>-1300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>7000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-500</v>
-      </c>
-      <c r="H102" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="I102" s="3">
-        <v>-300</v>
       </c>
       <c r="J102" s="3">
         <v>-1100</v>
       </c>
       <c r="K102" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L102" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="M102" s="3">
         <v>-1200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>3400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-200</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/HSCS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HSCS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="92">
   <si>
     <t>HSCS</t>
   </si>
@@ -656,102 +656,105 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45777</v>
+      </c>
+      <c r="E7" s="2">
         <v>45688</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45596</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45504</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45412</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45322</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45230</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45138</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45046</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44957</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44865</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44773</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44681</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44592</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44500</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44408</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44316</v>
       </c>
-      <c r="T7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -764,8 +767,8 @@
       <c r="F8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G8" s="3">
-        <v>0</v>
+      <c r="G8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H8" s="3">
         <v>0</v>
@@ -773,11 +776,11 @@
       <c r="I8" s="3">
         <v>0</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K8" s="3">
-        <v>0</v>
+      <c r="J8" s="3">
+        <v>0</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L8" s="3">
         <v>0</v>
@@ -812,13 +815,16 @@
       <c r="V8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>3</v>
+      <c r="D9" s="3">
+        <v>0</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>3</v>
@@ -826,8 +832,8 @@
       <c r="F9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G9" s="3">
-        <v>0</v>
+      <c r="G9" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H9" s="3">
         <v>0</v>
@@ -835,20 +841,20 @@
       <c r="I9" s="3">
         <v>0</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K9" s="3">
-        <v>0</v>
+      <c r="J9" s="3">
+        <v>0</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L9" s="3">
         <v>0</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N9" s="3">
-        <v>0</v>
+      <c r="M9" s="3">
+        <v>0</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O9" s="3">
         <v>0</v>
@@ -856,17 +862,17 @@
       <c r="P9" s="3">
         <v>0</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R9" s="3">
-        <v>0</v>
+      <c r="Q9" s="3">
+        <v>0</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S9" s="3">
         <v>0</v>
       </c>
-      <c r="T9" s="3" t="s">
-        <v>3</v>
+      <c r="T9" s="3">
+        <v>0</v>
       </c>
       <c r="U9" s="3" t="s">
         <v>3</v>
@@ -874,13 +880,16 @@
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>3</v>
+      <c r="D10" s="3">
+        <v>0</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>3</v>
@@ -888,8 +897,8 @@
       <c r="F10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G10" s="3">
-        <v>0</v>
+      <c r="G10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H10" s="3">
         <v>0</v>
@@ -897,20 +906,20 @@
       <c r="I10" s="3">
         <v>0</v>
       </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K10" s="3">
-        <v>0</v>
+      <c r="J10" s="3">
+        <v>0</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L10" s="3">
         <v>0</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N10" s="3">
-        <v>0</v>
+      <c r="M10" s="3">
+        <v>0</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O10" s="3">
         <v>0</v>
@@ -918,17 +927,17 @@
       <c r="P10" s="3">
         <v>0</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R10" s="3">
-        <v>0</v>
+      <c r="Q10" s="3">
+        <v>0</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S10" s="3">
         <v>0</v>
       </c>
-      <c r="T10" s="3" t="s">
-        <v>3</v>
+      <c r="T10" s="3">
+        <v>0</v>
       </c>
       <c r="U10" s="3" t="s">
         <v>3</v>
@@ -936,8 +945,11 @@
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -960,70 +972,74 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>900</v>
+      </c>
+      <c r="E12" s="3">
         <v>1000</v>
-      </c>
-      <c r="E12" s="3">
-        <v>1200</v>
       </c>
       <c r="F12" s="3">
         <v>1200</v>
       </c>
       <c r="G12" s="3">
+        <v>1200</v>
+      </c>
+      <c r="H12" s="3">
         <v>1000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>1400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>1600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>400</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>600</v>
       </c>
-      <c r="T12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1084,8 +1100,11 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1116,8 +1135,8 @@
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1126,19 +1145,19 @@
         <v>0</v>
       </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>-300</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>-300</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
-      <c r="T14" s="3" t="s">
-        <v>3</v>
+      <c r="T14" s="3">
+        <v>0</v>
       </c>
       <c r="U14" s="3" t="s">
         <v>3</v>
@@ -1146,8 +1165,11 @@
       <c r="V14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1208,8 +1230,11 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1229,132 +1254,139 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E17" s="3">
         <v>2400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>800</v>
       </c>
-      <c r="T17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E18" s="3">
         <v>-2400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-2000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-2100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-1900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-1500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-1600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-1300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-1600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-1300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-1800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-1400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-2000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-1000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-800</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1377,8 +1409,9 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1392,11 +1425,11 @@
         <v>0</v>
       </c>
       <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>-100</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
       <c r="I20" s="3">
         <v>0</v>
       </c>
@@ -1430,8 +1463,8 @@
       <c r="S20" s="3">
         <v>0</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
+      <c r="T20" s="3">
+        <v>0</v>
       </c>
       <c r="U20" s="3" t="s">
         <v>3</v>
@@ -1439,70 +1472,76 @@
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E21" s="3">
         <v>-2400</v>
-      </c>
-      <c r="E21" s="3">
-        <v>-2000</v>
       </c>
       <c r="F21" s="3">
         <v>-2000</v>
       </c>
       <c r="G21" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="H21" s="3">
         <v>-1800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-1500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-1600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-1300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-1600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-1300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-1800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-1400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-2000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-1000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-800</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1510,23 +1549,23 @@
         <v>200</v>
       </c>
       <c r="E22" s="3">
+        <v>200</v>
+      </c>
+      <c r="F22" s="3">
         <v>100</v>
       </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
       <c r="G22" s="3">
         <v>0</v>
       </c>
       <c r="H22" s="3">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3">
         <v>100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>200</v>
       </c>
-      <c r="J22" s="3">
-        <v>0</v>
-      </c>
       <c r="K22" s="3">
         <v>0</v>
       </c>
@@ -1537,16 +1576,16 @@
         <v>0</v>
       </c>
       <c r="N22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O22" s="3">
         <v>100</v>
       </c>
       <c r="P22" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q22" s="3">
         <v>300</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>100</v>
       </c>
       <c r="R22" s="3">
         <v>100</v>
@@ -1554,8 +1593,8 @@
       <c r="S22" s="3">
         <v>100</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>3</v>
+      <c r="T22" s="3">
+        <v>100</v>
       </c>
       <c r="U22" s="3" t="s">
         <v>3</v>
@@ -1563,70 +1602,76 @@
       <c r="V22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-2500</v>
-      </c>
-      <c r="E23" s="3">
-        <v>-2100</v>
       </c>
       <c r="F23" s="3">
         <v>-2100</v>
       </c>
       <c r="G23" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="H23" s="3">
         <v>-1800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-1600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-1700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-1400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-1600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-1300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-1800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-1600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-2100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-1000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-900</v>
       </c>
-      <c r="T23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1657,8 +1702,8 @@
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
+      <c r="M24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N24" s="3">
         <v>0</v>
@@ -1687,8 +1732,11 @@
       <c r="V24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1749,132 +1797,141 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-2500</v>
-      </c>
-      <c r="E26" s="3">
-        <v>-2100</v>
       </c>
       <c r="F26" s="3">
         <v>-2100</v>
       </c>
       <c r="G26" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="H26" s="3">
         <v>-1800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-1600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-1400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-1600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-1300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-1800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-1600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-2100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-1000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-900</v>
       </c>
-      <c r="T26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-2500</v>
-      </c>
-      <c r="E27" s="3">
-        <v>-2100</v>
       </c>
       <c r="F27" s="3">
         <v>-2100</v>
       </c>
       <c r="G27" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="H27" s="3">
         <v>-1800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-1600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-1400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-2100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-1000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-900</v>
       </c>
-      <c r="T27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1935,8 +1992,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1997,8 +2057,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2059,8 +2122,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2121,8 +2187,11 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2136,11 +2205,11 @@
         <v>0</v>
       </c>
       <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>100</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
       <c r="I32" s="3">
         <v>0</v>
       </c>
@@ -2174,8 +2243,8 @@
       <c r="S32" s="3">
         <v>0</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
+      <c r="T32" s="3">
+        <v>0</v>
       </c>
       <c r="U32" s="3" t="s">
         <v>3</v>
@@ -2183,70 +2252,76 @@
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-2500</v>
-      </c>
-      <c r="E33" s="3">
-        <v>-2100</v>
       </c>
       <c r="F33" s="3">
         <v>-2100</v>
       </c>
       <c r="G33" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="H33" s="3">
         <v>-1800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-1600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-1400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-1300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-1800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-2100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-1000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-900</v>
       </c>
-      <c r="T33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2307,137 +2382,146 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-2500</v>
-      </c>
-      <c r="E35" s="3">
-        <v>-2100</v>
       </c>
       <c r="F35" s="3">
         <v>-2100</v>
       </c>
       <c r="G35" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="H35" s="3">
         <v>-1800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-1600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-1400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-1300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-1800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-2100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-1000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-900</v>
       </c>
-      <c r="T35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45777</v>
+      </c>
+      <c r="E38" s="2">
         <v>45688</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45596</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45504</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45412</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45322</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45230</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45138</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45046</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44957</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44865</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44773</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44681</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44592</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44500</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44408</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44316</v>
       </c>
-      <c r="T38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2460,8 +2544,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2484,53 +2569,54 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E41" s="3">
         <v>2600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>4100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>5800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>7100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>4300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1300</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2546,8 +2632,11 @@
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2608,13 +2697,16 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>3</v>
+      <c r="D43" s="3">
+        <v>0</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>3</v>
@@ -2625,14 +2717,14 @@
       <c r="G43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H43" s="3">
-        <v>0</v>
+      <c r="H43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I43" s="3">
         <v>0</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
+      <c r="J43" s="3">
+        <v>0</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
@@ -2640,8 +2732,8 @@
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
+      <c r="M43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N43" s="3">
         <v>0</v>
@@ -2649,8 +2741,8 @@
       <c r="O43" s="3">
         <v>0</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>3</v>
+      <c r="P43" s="3">
+        <v>0</v>
       </c>
       <c r="Q43" s="3" t="s">
         <v>3</v>
@@ -2670,8 +2762,11 @@
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2682,13 +2777,13 @@
         <v>700</v>
       </c>
       <c r="F44" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="G44" s="3">
         <v>600</v>
       </c>
       <c r="H44" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="I44" s="3">
         <v>700</v>
@@ -2714,8 +2809,8 @@
       <c r="P44" s="3">
         <v>700</v>
       </c>
-      <c r="Q44" s="3" t="s">
-        <v>3</v>
+      <c r="Q44" s="3">
+        <v>700</v>
       </c>
       <c r="R44" s="3" t="s">
         <v>3</v>
@@ -2732,16 +2827,19 @@
       <c r="V44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>300</v>
+      </c>
+      <c r="E45" s="3">
         <v>200</v>
-      </c>
-      <c r="E45" s="3">
-        <v>700</v>
       </c>
       <c r="F45" s="3">
         <v>700</v>
@@ -2756,29 +2854,29 @@
         <v>700</v>
       </c>
       <c r="J45" s="3">
+        <v>700</v>
+      </c>
+      <c r="K45" s="3">
         <v>300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>200</v>
       </c>
-      <c r="L45" s="3">
-        <v>0</v>
-      </c>
       <c r="M45" s="3">
+        <v>0</v>
+      </c>
+      <c r="N45" s="3">
         <v>400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>400</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2794,53 +2892,56 @@
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E46" s="3">
         <v>3600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>6100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>7400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>8700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>4100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2400</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2856,8 +2957,11 @@
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2888,8 +2992,8 @@
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -2918,13 +3022,16 @@
       <c r="V47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="E48" s="3">
         <v>500</v>
@@ -2933,13 +3040,13 @@
         <v>500</v>
       </c>
       <c r="G48" s="3">
+        <v>500</v>
+      </c>
+      <c r="H48" s="3">
         <v>600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>500</v>
-      </c>
-      <c r="I48" s="3">
-        <v>600</v>
       </c>
       <c r="J48" s="3">
         <v>600</v>
@@ -2954,16 +3061,16 @@
         <v>600</v>
       </c>
       <c r="N48" s="3">
+        <v>600</v>
+      </c>
+      <c r="O48" s="3">
         <v>100</v>
-      </c>
-      <c r="O48" s="3">
-        <v>200</v>
       </c>
       <c r="P48" s="3">
         <v>200</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>3</v>
+      <c r="Q48" s="3">
+        <v>200</v>
       </c>
       <c r="R48" s="3" t="s">
         <v>3</v>
@@ -2980,8 +3087,11 @@
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3001,7 +3111,7 @@
         <v>1600</v>
       </c>
       <c r="I49" s="3">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="J49" s="3">
         <v>0</v>
@@ -3012,14 +3122,14 @@
       <c r="L49" s="3">
         <v>0</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>3</v>
+      <c r="M49" s="3">
+        <v>0</v>
       </c>
       <c r="N49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O49" s="3">
-        <v>0</v>
+      <c r="O49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P49" s="3">
         <v>0</v>
@@ -3042,8 +3152,11 @@
       <c r="V49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3104,8 +3217,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3166,8 +3282,11 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3198,8 +3317,8 @@
       <c r="L52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M52" s="3">
-        <v>0</v>
+      <c r="M52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N52" s="3">
         <v>0</v>
@@ -3228,8 +3347,11 @@
       <c r="V52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3290,53 +3412,56 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E54" s="3">
         <v>5700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>7800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>8200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>9500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>10800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>3500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>5600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2600</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3352,8 +3477,11 @@
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3376,8 +3504,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3400,19 +3529,20 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>300</v>
+      </c>
+      <c r="E57" s="3">
         <v>400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>300</v>
-      </c>
-      <c r="F57" s="3">
-        <v>400</v>
       </c>
       <c r="G57" s="3">
         <v>400</v>
@@ -3421,32 +3551,32 @@
         <v>400</v>
       </c>
       <c r="I57" s="3">
+        <v>400</v>
+      </c>
+      <c r="J57" s="3">
         <v>1100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>400</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3462,53 +3592,56 @@
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E58" s="3">
         <v>2600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>100</v>
-      </c>
-      <c r="G58" s="3">
-        <v>600</v>
       </c>
       <c r="H58" s="3">
         <v>600</v>
       </c>
       <c r="I58" s="3">
+        <v>600</v>
+      </c>
+      <c r="J58" s="3">
         <v>1500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1600</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>2600</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3524,53 +3657,56 @@
       <c r="V58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>0</v>
+      </c>
+      <c r="E59" s="3">
         <v>100</v>
-      </c>
-      <c r="E59" s="3">
-        <v>200</v>
       </c>
       <c r="F59" s="3">
         <v>200</v>
       </c>
       <c r="G59" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H59" s="3">
+        <v>0</v>
+      </c>
+      <c r="I59" s="3">
         <v>100</v>
-      </c>
-      <c r="I59" s="3">
-        <v>200</v>
       </c>
       <c r="J59" s="3">
         <v>200</v>
       </c>
       <c r="K59" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="L59" s="3">
+        <v>0</v>
+      </c>
+      <c r="M59" s="3">
         <v>200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1000</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3586,53 +3722,56 @@
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E60" s="3">
         <v>3600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>4100</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3648,8 +3787,11 @@
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3657,44 +3799,44 @@
         <v>300</v>
       </c>
       <c r="E61" s="3">
+        <v>300</v>
+      </c>
+      <c r="F61" s="3">
         <v>400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>400</v>
-      </c>
-      <c r="H61" s="3">
-        <v>500</v>
       </c>
       <c r="I61" s="3">
         <v>500</v>
       </c>
       <c r="J61" s="3">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="K61" s="3">
         <v>1000</v>
       </c>
       <c r="L61" s="3">
+        <v>1000</v>
+      </c>
+      <c r="M61" s="3">
         <v>1500</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3">
         <v>1000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>4400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2600</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -3710,19 +3852,22 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E62" s="3">
-        <v>0</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>3</v>
+      <c r="E62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F62" s="3">
+        <v>0</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>3</v>
@@ -3733,8 +3878,8 @@
       <c r="I62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J62" s="3">
-        <v>200</v>
+      <c r="J62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K62" s="3">
         <v>200</v>
@@ -3743,19 +3888,19 @@
         <v>200</v>
       </c>
       <c r="M62" s="3">
+        <v>200</v>
+      </c>
+      <c r="N62" s="3">
         <v>500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>200</v>
       </c>
-      <c r="P62" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q62" s="3" t="s">
-        <v>3</v>
+      <c r="Q62" s="3">
+        <v>0</v>
       </c>
       <c r="R62" s="3" t="s">
         <v>3</v>
@@ -3772,8 +3917,11 @@
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3834,8 +3982,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3896,8 +4047,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3958,53 +4112,56 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E66" s="3">
         <v>3900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2300</v>
-      </c>
-      <c r="G66" s="3">
-        <v>2200</v>
       </c>
       <c r="H66" s="3">
         <v>2200</v>
       </c>
       <c r="I66" s="3">
+        <v>2200</v>
+      </c>
+      <c r="J66" s="3">
         <v>4000</v>
-      </c>
-      <c r="J66" s="3">
-        <v>3100</v>
       </c>
       <c r="K66" s="3">
         <v>3100</v>
       </c>
       <c r="L66" s="3">
-        <v>3700</v>
+        <v>3100</v>
       </c>
       <c r="M66" s="3">
         <v>3700</v>
       </c>
       <c r="N66" s="3">
+        <v>3700</v>
+      </c>
+      <c r="O66" s="3">
         <v>2700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>8100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>6700</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4020,8 +4177,11 @@
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4044,8 +4204,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4106,8 +4267,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4168,8 +4332,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4230,8 +4397,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4292,53 +4462,56 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-76100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-74000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-71500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-69400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-67400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-65500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-63900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-62100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-60800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-59100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-57800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-56000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-54400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-52300</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4354,8 +4527,11 @@
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4416,8 +4592,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4478,8 +4657,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4540,53 +4722,56 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>200</v>
+      </c>
+      <c r="E76" s="3">
         <v>1800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>5900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>7300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>8600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-1700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-6100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-4100</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4602,8 +4787,11 @@
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4664,137 +4852,146 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45777</v>
+      </c>
+      <c r="E80" s="2">
         <v>45688</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45596</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45504</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45412</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45322</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45230</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45138</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45046</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44957</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44865</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44773</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44681</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44592</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44500</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44408</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44316</v>
       </c>
-      <c r="T80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-2500</v>
-      </c>
-      <c r="E81" s="3">
-        <v>-2100</v>
       </c>
       <c r="F81" s="3">
         <v>-2100</v>
       </c>
       <c r="G81" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="H81" s="3">
         <v>-1800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-1600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-1400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-1300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-1800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-2100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-1000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-900</v>
       </c>
-      <c r="T81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4817,8 +5014,9 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4832,11 +5030,11 @@
         <v>0</v>
       </c>
       <c r="G83" s="3">
+        <v>0</v>
+      </c>
+      <c r="H83" s="3">
         <v>100</v>
       </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
       <c r="I83" s="3">
         <v>0</v>
       </c>
@@ -4870,8 +5068,8 @@
       <c r="S83" s="3">
         <v>0</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>3</v>
+      <c r="T83" s="3">
+        <v>0</v>
       </c>
       <c r="U83" s="3" t="s">
         <v>3</v>
@@ -4879,8 +5077,11 @@
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4941,8 +5142,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5003,8 +5207,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5065,8 +5272,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5127,8 +5337,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5189,8 +5402,11 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -5198,52 +5414,52 @@
         <v>-1600</v>
       </c>
       <c r="E89" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="F89" s="3">
         <v>-2200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-2000</v>
       </c>
-      <c r="G89" s="3">
-        <v>-1500</v>
-      </c>
       <c r="H89" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="I89" s="3">
         <v>-2100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-1000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-1400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-1200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-800</v>
-      </c>
-      <c r="R89" s="3">
-        <v>-700</v>
       </c>
       <c r="S89" s="3">
         <v>-700</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>3</v>
+      <c r="T89" s="3">
+        <v>-700</v>
       </c>
       <c r="U89" s="3" t="s">
         <v>3</v>
@@ -5251,8 +5467,11 @@
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5275,8 +5494,9 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5286,11 +5506,11 @@
       <c r="E91" s="3">
         <v>0</v>
       </c>
-      <c r="F91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
+      <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H91" s="3">
         <v>0</v>
@@ -5298,11 +5518,11 @@
       <c r="I91" s="3">
         <v>0</v>
       </c>
-      <c r="J91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K91" s="3">
-        <v>0</v>
+      <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L91" s="3">
         <v>0</v>
@@ -5325,8 +5545,8 @@
       <c r="R91" s="3">
         <v>0</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>3</v>
+      <c r="S91" s="3">
+        <v>0</v>
       </c>
       <c r="T91" s="3" t="s">
         <v>3</v>
@@ -5337,8 +5557,11 @@
       <c r="V91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5399,8 +5622,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5461,8 +5687,11 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5476,11 +5705,11 @@
         <v>0</v>
       </c>
       <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
         <v>-100</v>
       </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
       <c r="I94" s="3">
         <v>0</v>
       </c>
@@ -5514,8 +5743,8 @@
       <c r="S94" s="3">
         <v>0</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>3</v>
+      <c r="T94" s="3">
+        <v>0</v>
       </c>
       <c r="U94" s="3" t="s">
         <v>3</v>
@@ -5523,8 +5752,11 @@
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5547,8 +5779,9 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5579,8 +5812,8 @@
       <c r="L96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -5609,8 +5842,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5671,8 +5907,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5733,8 +5972,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5795,70 +6037,76 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>100</v>
+      </c>
+      <c r="E100" s="3">
         <v>200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>9100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1600</v>
-      </c>
-      <c r="L100" s="3">
-        <v>-100</v>
       </c>
       <c r="M100" s="3">
         <v>-100</v>
       </c>
       <c r="N100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="O100" s="3">
         <v>5200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>3100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1100</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
       <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
         <v>500</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5889,8 +6137,8 @@
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -5919,8 +6167,11 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -5928,57 +6179,60 @@
         <v>-1500</v>
       </c>
       <c r="E102" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="F102" s="3">
         <v>-300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>7000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>3400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-200</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/HSCS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HSCS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="92">
   <si>
     <t>HSCS</t>
   </si>
@@ -656,109 +656,117 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46053</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45961</v>
+      </c>
+      <c r="F7" s="2">
         <v>45869</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45777</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45688</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45596</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45504</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45412</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45322</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45230</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45138</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45046</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44957</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44865</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44773</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44681</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44592</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44500</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44408</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44316</v>
       </c>
-      <c r="V7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="W7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -768,32 +776,32 @@
       <c r="E8" s="3">
         <v>0</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>3</v>
+      <c r="F8" s="3">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3">
-        <v>0</v>
+      <c r="I8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>3</v>
+      <c r="L8" s="3">
+        <v>0</v>
       </c>
       <c r="M8" s="3">
         <v>0</v>
       </c>
-      <c r="N8" s="3">
-        <v>0</v>
+      <c r="N8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O8" s="3">
         <v>0</v>
@@ -825,144 +833,162 @@
       <c r="X8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3">
-        <v>0</v>
+      <c r="D9" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E9" s="3">
         <v>0</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>3</v>
+      <c r="F9" s="3">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I9" s="3">
-        <v>0</v>
-      </c>
-      <c r="J9" s="3">
-        <v>0</v>
+      <c r="I9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K9" s="3">
         <v>0</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>3</v>
+      <c r="L9" s="3">
+        <v>0</v>
       </c>
       <c r="M9" s="3">
         <v>0</v>
       </c>
-      <c r="N9" s="3">
-        <v>0</v>
-      </c>
-      <c r="O9" s="3" t="s">
-        <v>3</v>
+      <c r="N9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O9" s="3">
+        <v>0</v>
       </c>
       <c r="P9" s="3">
         <v>0</v>
       </c>
-      <c r="Q9" s="3">
-        <v>0</v>
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R9" s="3">
         <v>0</v>
       </c>
-      <c r="S9" s="3" t="s">
-        <v>3</v>
+      <c r="S9" s="3">
+        <v>0</v>
       </c>
       <c r="T9" s="3">
         <v>0</v>
       </c>
-      <c r="U9" s="3">
-        <v>0</v>
-      </c>
-      <c r="V9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W9" s="3" t="s">
-        <v>3</v>
+      <c r="U9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V9" s="3">
+        <v>0</v>
+      </c>
+      <c r="W9" s="3">
+        <v>0</v>
       </c>
       <c r="X9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3">
-        <v>0</v>
+      <c r="D10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E10" s="3">
         <v>0</v>
       </c>
-      <c r="F10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
+      <c r="F10" s="3">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I10" s="3">
-        <v>0</v>
-      </c>
-      <c r="J10" s="3">
-        <v>0</v>
+      <c r="I10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K10" s="3">
         <v>0</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
+      <c r="L10" s="3">
+        <v>0</v>
       </c>
       <c r="M10" s="3">
         <v>0</v>
       </c>
-      <c r="N10" s="3">
-        <v>0</v>
-      </c>
-      <c r="O10" s="3" t="s">
-        <v>3</v>
+      <c r="N10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O10" s="3">
+        <v>0</v>
       </c>
       <c r="P10" s="3">
         <v>0</v>
       </c>
-      <c r="Q10" s="3">
-        <v>0</v>
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R10" s="3">
         <v>0</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>3</v>
+      <c r="S10" s="3">
+        <v>0</v>
       </c>
       <c r="T10" s="3">
         <v>0</v>
       </c>
-      <c r="U10" s="3">
-        <v>0</v>
-      </c>
-      <c r="V10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W10" s="3" t="s">
-        <v>3</v>
+      <c r="U10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V10" s="3">
+        <v>0</v>
+      </c>
+      <c r="W10" s="3">
+        <v>0</v>
       </c>
       <c r="X10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -987,76 +1013,84 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="E12" s="3">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="F12" s="3">
         <v>1000</v>
       </c>
       <c r="G12" s="3">
+        <v>900</v>
+      </c>
+      <c r="H12" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I12" s="3">
         <v>1200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>1200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>1000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>800</v>
-      </c>
-      <c r="L12" s="3">
-        <v>600</v>
-      </c>
-      <c r="M12" s="3">
-        <v>500</v>
       </c>
       <c r="N12" s="3">
         <v>600</v>
       </c>
       <c r="O12" s="3">
+        <v>500</v>
+      </c>
+      <c r="P12" s="3">
+        <v>600</v>
+      </c>
+      <c r="Q12" s="3">
         <v>800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>1400</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>1600</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>500</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>400</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>600</v>
       </c>
-      <c r="V12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1123,8 +1157,14 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1161,17 +1201,17 @@
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
       <c r="R14" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="S14" s="3">
         <v>0</v>
@@ -1182,17 +1222,23 @@
       <c r="U14" s="3">
         <v>0</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W14" s="3" t="s">
-        <v>3</v>
+      <c r="V14" s="3">
+        <v>-300</v>
+      </c>
+      <c r="W14" s="3">
+        <v>0</v>
       </c>
       <c r="X14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1259,8 +1305,14 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1282,8 +1334,10 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1291,28 +1345,28 @@
         <v>1900</v>
       </c>
       <c r="E17" s="3">
+        <v>2100</v>
+      </c>
+      <c r="F17" s="3">
         <v>1900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
+        <v>1900</v>
+      </c>
+      <c r="H17" s="3">
         <v>2400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>2000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>2100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>1900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>1500</v>
-      </c>
-      <c r="K17" s="3">
-        <v>1600</v>
-      </c>
-      <c r="L17" s="3">
-        <v>1300</v>
       </c>
       <c r="M17" s="3">
         <v>1600</v>
@@ -1321,37 +1375,43 @@
         <v>1300</v>
       </c>
       <c r="O17" s="3">
+        <v>1600</v>
+      </c>
+      <c r="P17" s="3">
+        <v>1300</v>
+      </c>
+      <c r="Q17" s="3">
         <v>1800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>1400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>2000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>2500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>1000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>800</v>
       </c>
-      <c r="V17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1359,28 +1419,28 @@
         <v>-1900</v>
       </c>
       <c r="E18" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="F18" s="3">
         <v>-1900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="H18" s="3">
         <v>-2400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-2000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-2100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-1900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-1500</v>
-      </c>
-      <c r="K18" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="L18" s="3">
-        <v>-1300</v>
       </c>
       <c r="M18" s="3">
         <v>-1600</v>
@@ -1389,37 +1449,43 @@
         <v>-1300</v>
       </c>
       <c r="O18" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="P18" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="Q18" s="3">
         <v>-1800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-2000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-2500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-1000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-800</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1444,8 +1510,10 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1465,14 +1533,14 @@
         <v>0</v>
       </c>
       <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>-100</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
         <v>0</v>
       </c>
@@ -1503,17 +1571,23 @@
       <c r="U20" s="3">
         <v>0</v>
       </c>
-      <c r="V20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W20" s="3" t="s">
-        <v>3</v>
+      <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
+        <v>0</v>
       </c>
       <c r="X20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1521,28 +1595,28 @@
         <v>-1900</v>
       </c>
       <c r="E21" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="F21" s="3">
         <v>-1900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="H21" s="3">
         <v>-2400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-2000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-2000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-1800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-1500</v>
-      </c>
-      <c r="K21" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="L21" s="3">
-        <v>-1300</v>
       </c>
       <c r="M21" s="3">
         <v>-1600</v>
@@ -1551,70 +1625,76 @@
         <v>-1300</v>
       </c>
       <c r="O21" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="P21" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="Q21" s="3">
         <v>-1800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-2000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-2500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-1000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>-400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>-800</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E22" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="F22" s="3">
         <v>200</v>
       </c>
       <c r="G22" s="3">
+        <v>200</v>
+      </c>
+      <c r="H22" s="3">
+        <v>200</v>
+      </c>
+      <c r="I22" s="3">
         <v>100</v>
       </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
       <c r="J22" s="3">
+        <v>0</v>
+      </c>
+      <c r="K22" s="3">
+        <v>0</v>
+      </c>
+      <c r="L22" s="3">
         <v>100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>200</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
-      <c r="M22" s="3">
-        <v>0</v>
-      </c>
       <c r="N22" s="3">
         <v>0</v>
       </c>
@@ -1622,102 +1702,114 @@
         <v>0</v>
       </c>
       <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3">
         <v>100</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>100</v>
-      </c>
-      <c r="R22" s="3">
-        <v>300</v>
       </c>
       <c r="S22" s="3">
         <v>100</v>
       </c>
       <c r="T22" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="U22" s="3">
         <v>100</v>
       </c>
-      <c r="V22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W22" s="3" t="s">
-        <v>3</v>
+      <c r="V22" s="3">
+        <v>100</v>
+      </c>
+      <c r="W22" s="3">
+        <v>100</v>
       </c>
       <c r="X22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="F23" s="3">
         <v>-2100</v>
-      </c>
-      <c r="E23" s="3">
-        <v>-2100</v>
-      </c>
-      <c r="F23" s="3">
-        <v>-2500</v>
       </c>
       <c r="G23" s="3">
         <v>-2100</v>
       </c>
       <c r="H23" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="I23" s="3">
         <v>-2100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="K23" s="3">
         <v>-1800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-1600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-1700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-1400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-1600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-1300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-1800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-2100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-2800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-1000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-900</v>
       </c>
-      <c r="V23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1754,11 +1846,11 @@
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
-      <c r="P24" s="3">
-        <v>0</v>
+      <c r="O24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q24" s="3">
         <v>0</v>
@@ -1784,8 +1876,14 @@
       <c r="X24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1852,144 +1950,162 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="F26" s="3">
         <v>-2100</v>
-      </c>
-      <c r="E26" s="3">
-        <v>-2100</v>
-      </c>
-      <c r="F26" s="3">
-        <v>-2500</v>
       </c>
       <c r="G26" s="3">
         <v>-2100</v>
       </c>
       <c r="H26" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="I26" s="3">
         <v>-2100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="K26" s="3">
         <v>-1800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-1600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-1700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-1400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-1600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-1300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-1800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-2100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-2800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-1000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-900</v>
       </c>
-      <c r="V26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="F27" s="3">
         <v>-2100</v>
-      </c>
-      <c r="E27" s="3">
-        <v>-2100</v>
-      </c>
-      <c r="F27" s="3">
-        <v>-2500</v>
       </c>
       <c r="G27" s="3">
         <v>-2100</v>
       </c>
       <c r="H27" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="I27" s="3">
         <v>-2100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="K27" s="3">
         <v>-1800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-1600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-1700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-1400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-1600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-1300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-1800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-2100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-2800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-1000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-900</v>
       </c>
-      <c r="V27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2056,8 +2172,14 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2124,8 +2246,14 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2192,8 +2320,14 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2260,8 +2394,14 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2281,14 +2421,14 @@
         <v>0</v>
       </c>
       <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>100</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
         <v>0</v>
       </c>
@@ -2319,85 +2459,97 @@
       <c r="U32" s="3">
         <v>0</v>
       </c>
-      <c r="V32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W32" s="3" t="s">
-        <v>3</v>
+      <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
+        <v>0</v>
       </c>
       <c r="X32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="F33" s="3">
         <v>-2100</v>
-      </c>
-      <c r="E33" s="3">
-        <v>-2100</v>
-      </c>
-      <c r="F33" s="3">
-        <v>-2500</v>
       </c>
       <c r="G33" s="3">
         <v>-2100</v>
       </c>
       <c r="H33" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="I33" s="3">
         <v>-2100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="K33" s="3">
         <v>-1800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-1600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-1700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-1400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-1600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-1300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-1800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-2100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-2800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-1000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-900</v>
       </c>
-      <c r="V33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2464,149 +2616,167 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="F35" s="3">
         <v>-2100</v>
-      </c>
-      <c r="E35" s="3">
-        <v>-2100</v>
-      </c>
-      <c r="F35" s="3">
-        <v>-2500</v>
       </c>
       <c r="G35" s="3">
         <v>-2100</v>
       </c>
       <c r="H35" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="I35" s="3">
         <v>-2100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="K35" s="3">
         <v>-1800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-1600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-1700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-1400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-1600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-1300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-1800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-2100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-2800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-1000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-900</v>
       </c>
-      <c r="V35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46053</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45961</v>
+      </c>
+      <c r="F38" s="2">
         <v>45869</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45777</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45688</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45596</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45504</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45412</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45322</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45230</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45138</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45046</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44957</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44865</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44773</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44681</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44592</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44500</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44408</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44316</v>
       </c>
-      <c r="V38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="W38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2631,8 +2801,10 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2657,62 +2829,64 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E41" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F41" s="3">
         <v>2800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>1100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>2600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>4100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>4300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>5800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>7100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>1700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>1900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>3100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>4300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>1300</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2725,8 +2899,14 @@
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2793,22 +2973,28 @@
       <c r="X42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E43" s="3">
-        <v>0</v>
+      <c r="E43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>3</v>
+      <c r="G43" s="3">
+        <v>0</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>3</v>
@@ -2816,35 +3002,35 @@
       <c r="I43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J43" s="3">
-        <v>0</v>
-      </c>
-      <c r="K43" s="3">
-        <v>0</v>
-      </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M43" s="3" t="s">
-        <v>3</v>
+      <c r="J43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L43" s="3">
+        <v>0</v>
+      </c>
+      <c r="M43" s="3">
+        <v>0</v>
       </c>
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O43" s="3">
-        <v>0</v>
-      </c>
-      <c r="P43" s="3">
-        <v>0</v>
+      <c r="O43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q43" s="3">
         <v>0</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S43" s="3" t="s">
-        <v>3</v>
+      <c r="R43" s="3">
+        <v>0</v>
+      </c>
+      <c r="S43" s="3">
+        <v>0</v>
       </c>
       <c r="T43" s="3" t="s">
         <v>3</v>
@@ -2861,34 +3047,40 @@
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="E44" s="3">
         <v>700</v>
       </c>
       <c r="F44" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="G44" s="3">
         <v>700</v>
       </c>
       <c r="H44" s="3">
+        <v>700</v>
+      </c>
+      <c r="I44" s="3">
+        <v>700</v>
+      </c>
+      <c r="J44" s="3">
         <v>600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>600</v>
-      </c>
-      <c r="J44" s="3">
-        <v>700</v>
-      </c>
-      <c r="K44" s="3">
-        <v>700</v>
       </c>
       <c r="L44" s="3">
         <v>700</v>
@@ -2911,11 +3103,11 @@
       <c r="R44" s="3">
         <v>700</v>
       </c>
-      <c r="S44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T44" s="3" t="s">
-        <v>3</v>
+      <c r="S44" s="3">
+        <v>700</v>
+      </c>
+      <c r="T44" s="3">
+        <v>700</v>
       </c>
       <c r="U44" s="3" t="s">
         <v>3</v>
@@ -2929,25 +3121,31 @@
       <c r="X44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>900</v>
+      </c>
+      <c r="E45" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F45" s="3">
         <v>600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>200</v>
-      </c>
-      <c r="G45" s="3">
-        <v>700</v>
-      </c>
-      <c r="H45" s="3">
-        <v>700</v>
       </c>
       <c r="I45" s="3">
         <v>700</v>
@@ -2959,32 +3157,32 @@
         <v>700</v>
       </c>
       <c r="L45" s="3">
+        <v>700</v>
+      </c>
+      <c r="M45" s="3">
+        <v>700</v>
+      </c>
+      <c r="N45" s="3">
         <v>300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>200</v>
       </c>
-      <c r="N45" s="3">
-        <v>0</v>
-      </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="3">
         <v>400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>400</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2997,62 +3195,68 @@
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E46" s="3">
+        <v>3800</v>
+      </c>
+      <c r="F46" s="3">
         <v>4400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>2200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>3600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>5700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>6100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>7400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>8700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>1800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>2000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>2700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>2900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>4100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>5400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>1900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>2400</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3065,8 +3269,14 @@
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3103,11 +3313,11 @@
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -3133,28 +3343,34 @@
       <c r="X47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="E48" s="3">
         <v>400</v>
       </c>
       <c r="F48" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="G48" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="H48" s="3">
         <v>500</v>
       </c>
       <c r="I48" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="J48" s="3">
         <v>500</v>
@@ -3163,7 +3379,7 @@
         <v>600</v>
       </c>
       <c r="L48" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="M48" s="3">
         <v>600</v>
@@ -3175,20 +3391,20 @@
         <v>600</v>
       </c>
       <c r="P48" s="3">
+        <v>600</v>
+      </c>
+      <c r="Q48" s="3">
+        <v>600</v>
+      </c>
+      <c r="R48" s="3">
         <v>100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>200</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3201,16 +3417,22 @@
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>1600</v>
+        <v>2100</v>
       </c>
       <c r="E49" s="3">
-        <v>1600</v>
+        <v>1800</v>
       </c>
       <c r="F49" s="3">
         <v>1600</v>
@@ -3228,10 +3450,10 @@
         <v>1600</v>
       </c>
       <c r="K49" s="3">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="L49" s="3">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="M49" s="3">
         <v>0</v>
@@ -3239,17 +3461,17 @@
       <c r="N49" s="3">
         <v>0</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q49" s="3">
-        <v>0</v>
-      </c>
-      <c r="R49" s="3">
-        <v>0</v>
+      <c r="O49" s="3">
+        <v>0</v>
+      </c>
+      <c r="P49" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S49" s="3">
         <v>0</v>
@@ -3269,8 +3491,14 @@
       <c r="X49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3337,8 +3565,14 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3405,8 +3639,14 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3443,11 +3683,11 @@
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O52" s="3">
-        <v>0</v>
-      </c>
-      <c r="P52" s="3">
-        <v>0</v>
+      <c r="O52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q52" s="3">
         <v>0</v>
@@ -3473,8 +3713,14 @@
       <c r="X52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3541,62 +3787,68 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E54" s="3">
+        <v>6000</v>
+      </c>
+      <c r="F54" s="3">
         <v>6400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>4200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>5700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>7800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>8200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>9500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>10800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>2400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>2600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>3300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>3500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>4800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>5600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>2100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>2600</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3609,8 +3861,14 @@
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3635,8 +3893,10 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3661,19 +3921,21 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="E57" s="3">
         <v>300</v>
       </c>
       <c r="F57" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="G57" s="3">
         <v>300</v>
@@ -3682,41 +3944,41 @@
         <v>400</v>
       </c>
       <c r="I57" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="J57" s="3">
         <v>400</v>
       </c>
       <c r="K57" s="3">
+        <v>400</v>
+      </c>
+      <c r="L57" s="3">
+        <v>400</v>
+      </c>
+      <c r="M57" s="3">
         <v>1100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>1000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>400</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3729,62 +3991,68 @@
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E58" s="3">
+        <v>600</v>
+      </c>
+      <c r="F58" s="3">
         <v>1700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>2700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>2600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>2500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>600</v>
-      </c>
-      <c r="J58" s="3">
-        <v>600</v>
-      </c>
-      <c r="K58" s="3">
-        <v>1500</v>
       </c>
       <c r="L58" s="3">
         <v>600</v>
       </c>
       <c r="M58" s="3">
+        <v>1500</v>
+      </c>
+      <c r="N58" s="3">
+        <v>600</v>
+      </c>
+      <c r="O58" s="3">
         <v>500</v>
-      </c>
-      <c r="N58" s="3">
-        <v>100</v>
-      </c>
-      <c r="O58" s="3">
-        <v>1100</v>
       </c>
       <c r="P58" s="3">
         <v>100</v>
       </c>
       <c r="Q58" s="3">
+        <v>1100</v>
+      </c>
+      <c r="R58" s="3">
+        <v>100</v>
+      </c>
+      <c r="S58" s="3">
         <v>1600</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>2600</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3797,61 +4065,67 @@
       <c r="X58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>100</v>
+      </c>
+      <c r="E59" s="3">
+        <v>100</v>
+      </c>
+      <c r="F59" s="3">
         <v>200</v>
       </c>
-      <c r="E59" s="3">
-        <v>0</v>
-      </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
+        <v>0</v>
+      </c>
+      <c r="H59" s="3">
         <v>100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>200</v>
       </c>
-      <c r="I59" s="3">
-        <v>0</v>
-      </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
+        <v>0</v>
+      </c>
+      <c r="L59" s="3">
         <v>100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>200</v>
-      </c>
-      <c r="L59" s="3">
-        <v>200</v>
-      </c>
-      <c r="M59" s="3">
-        <v>0</v>
       </c>
       <c r="N59" s="3">
         <v>200</v>
       </c>
       <c r="O59" s="3">
+        <v>0</v>
+      </c>
+      <c r="P59" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q59" s="3">
         <v>1200</v>
-      </c>
-      <c r="P59" s="3">
-        <v>1000</v>
-      </c>
-      <c r="Q59" s="3">
-        <v>1100</v>
       </c>
       <c r="R59" s="3">
         <v>1000</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T59" s="3" t="s">
-        <v>3</v>
+      <c r="S59" s="3">
+        <v>1100</v>
+      </c>
+      <c r="T59" s="3">
+        <v>1000</v>
       </c>
       <c r="U59" s="3" t="s">
         <v>3</v>
@@ -3865,62 +4139,68 @@
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E60" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F60" s="3">
         <v>3000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>3700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>3600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>3300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>1400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>1800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>1700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>3500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>1900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>1800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>2000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>3100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>1500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>3500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>4100</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3933,62 +4213,68 @@
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="E61" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="F61" s="3">
         <v>300</v>
       </c>
       <c r="G61" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="H61" s="3">
-        <v>900</v>
+        <v>300</v>
       </c>
       <c r="I61" s="3">
         <v>400</v>
       </c>
       <c r="J61" s="3">
+        <v>900</v>
+      </c>
+      <c r="K61" s="3">
+        <v>400</v>
+      </c>
+      <c r="L61" s="3">
         <v>500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>1000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>1000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>1500</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3">
         <v>1000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>4400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>2600</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
         <v>0</v>
       </c>
@@ -4001,8 +4287,14 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4015,14 +4307,14 @@
       <c r="F62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G62" s="3">
-        <v>0</v>
+      <c r="G62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>3</v>
+      <c r="I62" s="3">
+        <v>0</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>3</v>
@@ -4030,32 +4322,32 @@
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L62" s="3">
-        <v>200</v>
-      </c>
-      <c r="M62" s="3">
-        <v>200</v>
+      <c r="L62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N62" s="3">
         <v>200</v>
       </c>
       <c r="O62" s="3">
+        <v>200</v>
+      </c>
+      <c r="P62" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q62" s="3">
         <v>500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>200</v>
       </c>
-      <c r="R62" s="3">
-        <v>0</v>
-      </c>
-      <c r="S62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T62" s="3" t="s">
-        <v>3</v>
+      <c r="T62" s="3">
+        <v>0</v>
       </c>
       <c r="U62" s="3" t="s">
         <v>3</v>
@@ -4069,8 +4361,14 @@
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4137,8 +4435,14 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4205,8 +4509,14 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4273,62 +4583,68 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E66" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F66" s="3">
         <v>3300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>4000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>3900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>3800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>2300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>2200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>2200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>4000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>3100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>3100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>3700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>3700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>2700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>8100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>6700</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4341,8 +4657,14 @@
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4367,8 +4689,10 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4435,8 +4759,14 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4503,8 +4833,14 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4571,8 +4907,14 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4639,62 +4981,68 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-82500</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-80500</v>
+      </c>
+      <c r="F72" s="3">
         <v>-78200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-76100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-74000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-71500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-69400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-67400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-65500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-63900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-62100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-60800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-59100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-57800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-56000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-54400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-52300</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4707,8 +5055,14 @@
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4775,8 +5129,14 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4843,8 +5203,14 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4911,62 +5277,68 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E76" s="3">
+        <v>4200</v>
+      </c>
+      <c r="F76" s="3">
         <v>3100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>1800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>4000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>5900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>7300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>8600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>-1700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>-500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>-300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>1100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>2900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>-6100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>-4100</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4979,8 +5351,14 @@
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5047,149 +5425,167 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46053</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45961</v>
+      </c>
+      <c r="F80" s="2">
         <v>45869</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45777</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45688</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45596</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45504</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45412</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45322</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45230</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45138</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45046</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44957</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44865</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44773</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44681</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44592</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44500</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44408</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44316</v>
       </c>
-      <c r="V80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="W80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="F81" s="3">
         <v>-2100</v>
-      </c>
-      <c r="E81" s="3">
-        <v>-2100</v>
-      </c>
-      <c r="F81" s="3">
-        <v>-2500</v>
       </c>
       <c r="G81" s="3">
         <v>-2100</v>
       </c>
       <c r="H81" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="I81" s="3">
         <v>-2100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="K81" s="3">
         <v>-1800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-1600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-1700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-1400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-1600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-1300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-1800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-2100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-2800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-1000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-900</v>
       </c>
-      <c r="V81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5214,8 +5610,10 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5235,14 +5633,14 @@
         <v>0</v>
       </c>
       <c r="I83" s="3">
+        <v>0</v>
+      </c>
+      <c r="J83" s="3">
+        <v>0</v>
+      </c>
+      <c r="K83" s="3">
         <v>100</v>
       </c>
-      <c r="J83" s="3">
-        <v>0</v>
-      </c>
-      <c r="K83" s="3">
-        <v>0</v>
-      </c>
       <c r="L83" s="3">
         <v>0</v>
       </c>
@@ -5273,17 +5671,23 @@
       <c r="U83" s="3">
         <v>0</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W83" s="3" t="s">
-        <v>3</v>
+      <c r="V83" s="3">
+        <v>0</v>
+      </c>
+      <c r="W83" s="3">
+        <v>0</v>
       </c>
       <c r="X83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5350,8 +5754,14 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5418,8 +5828,14 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5486,8 +5902,14 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5554,8 +5976,14 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5622,76 +6050,88 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="F89" s="3">
         <v>-2000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-1600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-1600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-2200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-2000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-1600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-2100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-1000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-1400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-1900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-1000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-1100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-1200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-2500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-700</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5716,43 +6156,45 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>3</v>
+      <c r="D91" s="3">
+        <v>0</v>
       </c>
       <c r="E91" s="3">
         <v>0</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
+      <c r="F91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G91" s="3">
         <v>0</v>
       </c>
-      <c r="H91" s="3" t="s">
-        <v>3</v>
+      <c r="H91" s="3">
+        <v>0</v>
       </c>
       <c r="I91" s="3">
         <v>0</v>
       </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="J91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>3</v>
+      <c r="L91" s="3">
+        <v>0</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
+      <c r="N91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O91" s="3">
         <v>0</v>
@@ -5772,11 +6214,11 @@
       <c r="T91" s="3">
         <v>0</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V91" s="3" t="s">
-        <v>3</v>
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
+        <v>0</v>
       </c>
       <c r="W91" s="3" t="s">
         <v>3</v>
@@ -5784,8 +6226,14 @@
       <c r="X91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5852,8 +6300,14 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5920,8 +6374,14 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5941,14 +6401,14 @@
         <v>0</v>
       </c>
       <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
         <v>-100</v>
       </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
       <c r="L94" s="3">
         <v>0</v>
       </c>
@@ -5979,17 +6439,23 @@
       <c r="U94" s="3">
         <v>0</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W94" s="3" t="s">
-        <v>3</v>
+      <c r="V94" s="3">
+        <v>0</v>
+      </c>
+      <c r="W94" s="3">
+        <v>0</v>
       </c>
       <c r="X94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6014,8 +6480,10 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6052,11 +6520,11 @@
       <c r="N96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -6082,8 +6550,14 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6150,8 +6624,14 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6218,8 +6698,14 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6286,76 +6772,88 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E100" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F100" s="3">
         <v>3600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>1900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>9100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>1600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>5200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>3100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>1100</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
         <v>500</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6392,11 +6890,11 @@
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -6422,72 +6920,84 @@
       <c r="X101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-800</v>
+      </c>
+      <c r="F102" s="3">
         <v>1700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-1500</v>
-      </c>
-      <c r="F102" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="G102" s="3">
-        <v>-300</v>
       </c>
       <c r="H102" s="3">
         <v>-1500</v>
       </c>
       <c r="I102" s="3">
+        <v>-300</v>
+      </c>
+      <c r="J102" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="K102" s="3">
         <v>-1300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>7000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-500</v>
-      </c>
-      <c r="L102" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="M102" s="3">
-        <v>-300</v>
       </c>
       <c r="N102" s="3">
         <v>-1100</v>
       </c>
       <c r="O102" s="3">
+        <v>-300</v>
+      </c>
+      <c r="P102" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="Q102" s="3">
         <v>-1200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>3400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-200</v>
       </c>
-      <c r="V102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
